--- a/Gmail_Inbox_Logger.xlsx
+++ b/Gmail_Inbox_Logger.xlsx
@@ -5,29 +5,35 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gmail_Inbox_Logger\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gmail_Inbox_Logger_n8n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9203A25-9C0F-4F04-84C4-73AB565100C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D0A465-9DE8-4A27-B042-0641B43B7269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Logs" sheetId="4" r:id="rId1"/>
-    <sheet name="📊 Dashboard" sheetId="2" r:id="rId2"/>
-    <sheet name="🔧 n8n Setup Guide" sheetId="3" r:id="rId3"/>
+    <sheet name="Logs" sheetId="2" r:id="rId1"/>
+    <sheet name="📊 Dashboard" sheetId="3" r:id="rId2"/>
+    <sheet name="🔧 n8n Setup Guide" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="259">
   <si>
     <t>📅 Date</t>
   </si>
@@ -303,6 +309,273 @@
   </si>
   <si>
     <t>You have used 13.5 GB of your 15 GB</t>
+  </si>
+  <si>
+    <t>Coursera@m.learn.coursera.org</t>
+  </si>
+  <si>
+    <t>Ends soon: Top courses at ₹7,499/year</t>
+  </si>
+  <si>
+    <t>Midyear is the perfect time to reset and build new skills. ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌</t>
+  </si>
+  <si>
+    <t>CATEGORY_PROMOTIONS</t>
+  </si>
+  <si>
+    <t>Emergent</t>
+  </si>
+  <si>
+    <t>team@ship.emergent.sh</t>
+  </si>
+  <si>
+    <t>A few project ideas to get you started</t>
+  </si>
+  <si>
+    <t>emergent A few projects to get you started We put together a few small projects you could get started with on Emergent. Everything from building a 3D website to Chrome extensions that could supercharge</t>
+  </si>
+  <si>
+    <t>CATEGORY_UPDATES</t>
+  </si>
+  <si>
+    <t>Agoda Price Alerts</t>
+  </si>
+  <si>
+    <t>no-reply@sg.newsletter.agoda-emails.com</t>
+  </si>
+  <si>
+    <t>Saksham, top price drops in New Delhi, selected for you!</t>
+  </si>
+  <si>
+    <t>Check out today's top price drops on Agoda! Agoda.com Hotels &amp; Homes Flights Deals Airport Transfer Activities Saksham, experience the best of New Delhi Your journey starts here! New Delhi July</t>
+  </si>
+  <si>
+    <t>updates-noreply@linkedin.com</t>
+  </si>
+  <si>
+    <t>Altaf Mohammad and others share their thoughts on LinkedIn</t>
+  </si>
+  <si>
+    <t>Learning DFT – Scan Verification Today, I spent some time learning about Scan… ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏</t>
+  </si>
+  <si>
+    <t>Sneha Kapoor</t>
+  </si>
+  <si>
+    <t>noreply@unstop.news</t>
+  </si>
+  <si>
+    <t>CII Post-Harvest Hackathon | National Recognition + Mentorship + Industry Exposure</t>
+  </si>
+  <si>
+    <t>Apply now! ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿</t>
+  </si>
+  <si>
+    <t>Sweatcoin</t>
+  </si>
+  <si>
+    <t>em@tra.sweatco.in</t>
+  </si>
+  <si>
+    <t>40 Sweatcoins are waiting 👀</t>
+  </si>
+  <si>
+    <t>Your next invite could be your easiest reward. Hey Saksham, If you've been thinking about inviting someone to Sweatcoin, now's a good time. Invite a friend and receive 40 Sweatcoins once they</t>
+  </si>
+  <si>
+    <t>Starbucks India</t>
+  </si>
+  <si>
+    <t>info@members.tatastarbucks.net</t>
+  </si>
+  <si>
+    <t>Welcome to green tier! Enjoy faster rewards and more choices to reedeem it.</t>
+  </si>
+  <si>
+    <t>Logo Logo Check Reward Status Reload Card Check Balance Explore Now Download the Starbucks ® India mobile app to simply scan and pay for your coffee at any Starbucks store in India. Image Image Find us</t>
+  </si>
+  <si>
+    <t>mail@em.sweatco.in</t>
+  </si>
+  <si>
+    <t>Saksham, did you finish the challenge?</t>
+  </si>
+  <si>
+    <t>See if you won the Win a $100 Rebel gift card! 🎉 🏆 ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿</t>
+  </si>
+  <si>
+    <t>Freelancer.com</t>
+  </si>
+  <si>
+    <t>noreply@notifications.freelancer.com</t>
+  </si>
+  <si>
+    <t>Saksham, these Video Editing, After Effects, and Adobe Premiere Pro projects and contests might interest you</t>
+  </si>
+  <si>
+    <t>Hi Saksham, Here are the latest projects and contests matching your skills: PROJECT DESCRIPTION BUDGET Minimal Poster &amp; Video Editing I'm looking for a creative partner to handle two related</t>
+  </si>
+  <si>
+    <t>Jia from Unstop</t>
+  </si>
+  <si>
+    <t>Earn stipend up to ₹50,000!</t>
+  </si>
+  <si>
+    <t>Top wfh opportunities! ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿</t>
+  </si>
+  <si>
+    <t>SBI</t>
+  </si>
+  <si>
+    <t>sbi@communications.sbi.co.in</t>
+  </si>
+  <si>
+    <t>Amazon Prime Day is Here – Enjoy 10% Instant Discount with SBI Debit Card</t>
+  </si>
+  <si>
+    <t>Dear Saksham, The biggest shopping days are here! Make the most of Amazon Prime Day with your SBI Debit Card and unlock instant savings, exciting offers, and additional rewards on your purchases. Shop</t>
+  </si>
+  <si>
+    <t>Rhea</t>
+  </si>
+  <si>
+    <t>Your AI mock tests are ready!</t>
+  </si>
+  <si>
+    <t>Prepare for Cisco, Wipro &amp; more. Tap to get started. ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏</t>
+  </si>
+  <si>
+    <t>👤 Saksham, add Samriddhi Ambadkar</t>
+  </si>
+  <si>
+    <t>Regional HR- Delhi NCR || Deputy Manager || HR Professional ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏</t>
+  </si>
+  <si>
+    <t>CATEGORY_SOCIAL</t>
+  </si>
+  <si>
+    <t>New skill available: Puzzle solving 🧩</t>
+  </si>
+  <si>
+    <t>Millions of professionals are already testing their skills with LinkedIn's daily puzzle games ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏</t>
+  </si>
+  <si>
+    <t>MBA applications close today: IIT Roorkee and O.P. Jindal</t>
+  </si>
+  <si>
+    <t>Don't miss today's application deadline! ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏ ‌ ﻿ ͏</t>
+  </si>
+  <si>
+    <t>Apply Now: Top internships &amp; hackathons open!</t>
+  </si>
+  <si>
+    <t>Your profile is a perfect match! ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏</t>
+  </si>
+  <si>
+    <t>Saksham, these Video Editing, Video Production, and Video Services projects might interest you</t>
+  </si>
+  <si>
+    <t>Hi Saksham, Here are the latest projects matching your skills: PROJECT DESCRIPTION BUDGET Looking to Purchase Industrial CCTV / Safety Violation Video Library I am looking to purchase an existing</t>
+  </si>
+  <si>
+    <t>Kaggle</t>
+  </si>
+  <si>
+    <t>no-reply@kaggle.com</t>
+  </si>
+  <si>
+    <t>Competition Launch: Biohub - Cell Tracking During Development</t>
+  </si>
+  <si>
+    <t>Hi Saksham1232, Scientists use 3D microscopy to study cells over time, but turning these images into insights is difficult. Thousands of cells move, divide, and change shape during large experiments,</t>
+  </si>
+  <si>
+    <t>Divy Jajodia and others share their thoughts on LinkedIn</t>
+  </si>
+  <si>
+    <t>Undergraduate Portfolio (selected works 2021-2026)🎓 Architecture, to me, is… ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏</t>
+  </si>
+  <si>
+    <t>Saksham, top price drops in Rishikesh, selected for you!</t>
+  </si>
+  <si>
+    <t>Check out today's top price drops on Agoda! Agoda.com Hotels &amp; Homes Flights Deals Airport Transfer Activities Saksham, experience the best of Rishikesh Your journey starts here! Rishikesh July</t>
+  </si>
+  <si>
+    <t>Big Grocery Savings, Delivered Fast</t>
+  </si>
+  <si>
+    <t>Dear Saksham, One simple mantra for smarter grocery shopping. More essentials, less expense. With BigBasket and your SBI Debit Card, you can enjoy instant discounts every time you stock up on your</t>
+  </si>
+  <si>
+    <t>Smriti Goel</t>
+  </si>
+  <si>
+    <t>Deadline Extended | Win Internships with Dabur, Ogilvy &amp; ₹5L+ in Prizes</t>
+  </si>
+  <si>
+    <t>Apply Now! ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿</t>
+  </si>
+  <si>
+    <t>alerts@info.sweatco.in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Saksham, you're 20% more active this week! </t>
+  </si>
+  <si>
+    <t>You took a total of 21729 steps ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿</t>
+  </si>
+  <si>
+    <t>Use AI</t>
+  </si>
+  <si>
+    <t>hello@use.ai</t>
+  </si>
+  <si>
+    <t>Our last email about Use AI</t>
+  </si>
+  <si>
+    <t>The question you asked is still waiting… ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏ ͏</t>
+  </si>
+  <si>
+    <t>Resumly</t>
+  </si>
+  <si>
+    <t>hello@notify.resumly.ai</t>
+  </si>
+  <si>
+    <t>7 fresh roles from the last 24 hours!</t>
+  </si>
+  <si>
+    <t>Fresh roles from the last 24 hours 7 roles posted in the last 24 hours that we think you'll like. Kaleris Associate Software Engineer Chennai, Tamil Nadu, IndiaFull time8 hrs ago Apply now → AP</t>
+  </si>
+  <si>
+    <t>Security, strengthened with Yono e-Secure lock. Try now!</t>
+  </si>
+  <si>
+    <t>Login Android button Login Apple button Terms &amp; Conditions apply* Disclaimer: Please note on clicking buttons/text mentioned above, you will be redirected to the related URLs links listed below.</t>
+  </si>
+  <si>
+    <t>Saksham, the results are in!</t>
+  </si>
+  <si>
+    <t>See if you won the Jersey 9 Challenge 🏆 ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿ ͏ ﻿</t>
+  </si>
+  <si>
+    <t>Hi Saksham, Here are the latest projects matching your skills: PROJECT DESCRIPTION BUDGET Creación de Videos Cortos Sobre Salud Mental - SOLO ESPAÑOL NATIVO Buscamos una persona para crear videos</t>
+  </si>
+  <si>
+    <t>OpenAI</t>
+  </si>
+  <si>
+    <t>noreply@tm.openai.com</t>
+  </si>
+  <si>
+    <t>Your Plus access will end soon</t>
+  </si>
+  <si>
+    <t>ChatGPT Update your payment method to keep using Plus Update payment Please update your payment method to keep access to Plus benefits: Extended limits on messaging, file uploads, and voice mode More</t>
   </si>
   <si>
     <t>📊  Gmail Analytics Dashboard</t>
@@ -543,96 +816,108 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd\ mmm\ yyyy"/>
+  </numFmts>
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF94A3B8"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0F172A"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF0F172A"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF16A34A"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFDC2626"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFEA580C"/>
       <name val="Arial"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="22"/>
       <color rgb="FF0F172A"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="18">
@@ -645,101 +930,122 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
+        <bgColor rgb="FF1E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F172A"/>
         <bgColor rgb="FF0F172A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0F172A"/>
-        <bgColor rgb="FF1E293B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEA580C"/>
-        <bgColor rgb="FFDC2626"/>
+        <bgColor rgb="FFEA580C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
         <bgColor rgb="FFF8FAFC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDCFCE7"/>
-        <bgColor rgb="FFF0FDF4"/>
+        <bgColor rgb="FFDCFCE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFEF9C3"/>
+        <bgColor rgb="FFFEF9C3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEE2E2"/>
+        <bgColor rgb="FFFEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBEAFE"/>
+        <bgColor rgb="FFDBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE7F3"/>
+        <bgColor rgb="FFFCE7F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F3FF"/>
+        <bgColor rgb="FFF5F3FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D4ED8"/>
+        <bgColor rgb="FF1D4ED8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF16A34A"/>
+        <bgColor rgb="FF16A34A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
         <bgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEE2E2"/>
-        <bgColor rgb="FFFCE7F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBEAFE"/>
-        <bgColor rgb="FFE2E8F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE7F3"/>
-        <bgColor rgb="FFFEE2E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F3FF"/>
+        <fgColor rgb="FFEFF6FF"/>
         <bgColor rgb="FFEFF6FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D4ED8"/>
-        <bgColor rgb="FF3366FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF16A34A"/>
-        <bgColor rgb="FF008080"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
-        <bgColor rgb="FFF8FAFC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF6FF"/>
-        <bgColor rgb="FFF5F3FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF0FDF4"/>
-        <bgColor rgb="FFF8FAFC"/>
+        <bgColor rgb="FFF0FDF4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -775,143 +1081,173 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFEA580C"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFEA580C"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="18" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -919,74 +1255,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFDC2626"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFFCE7F3"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFEF9C3"/>
-      <rgbColor rgb="FFDCFCE7"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF1D4ED8"/>
-      <rgbColor rgb="FFE2E8F0"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFDBEAFE"/>
-      <rgbColor rgb="FFF0FDF4"/>
-      <rgbColor rgb="FFFFF7ED"/>
-      <rgbColor rgb="FFEFF6FF"/>
-      <rgbColor rgb="FFF5F3FF"/>
-      <rgbColor rgb="FFF8FAFC"/>
-      <rgbColor rgb="FFFEE2E2"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFEA580C"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF94A3B8"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF16A34A"/>
-      <rgbColor rgb="FF0F172A"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF1E293B"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -999,9 +1267,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
@@ -1009,10 +1277,10 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="4F81BD"/>
@@ -1036,78 +1304,100 @@
         <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="0000FF"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1118,54 +1408,51 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-          <a:tileRect/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-          <a:tileRect/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1176,1041 +1463,4749 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E70852BB-5508-442E-A11A-02B24C057702}">
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H1003"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="36.77734375" customWidth="1"/>
-    <col min="2" max="2" width="42.77734375" customWidth="1"/>
-    <col min="3" max="3" width="48.77734375" customWidth="1"/>
+    <col min="1" max="1" width="36.6640625" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" customWidth="1"/>
+    <col min="3" max="3" width="48.6640625" customWidth="1"/>
     <col min="4" max="4" width="57.109375" customWidth="1"/>
     <col min="5" max="5" width="64.88671875" customWidth="1"/>
-    <col min="6" max="6" width="66.77734375" customWidth="1"/>
-    <col min="7" max="7" width="68.77734375" customWidth="1"/>
+    <col min="6" max="6" width="66.6640625" customWidth="1"/>
+    <col min="7" max="7" width="68.6640625" customWidth="1"/>
     <col min="8" max="8" width="77.6640625" customWidth="1"/>
+    <col min="9" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="66" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
+    <row r="3" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="66" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+    <row r="5" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+    <row r="7" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="H8" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
+    <row r="9" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+    <row r="10" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+    <row r="11" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="66" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+    <row r="12" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G12" s="17" t="s">
+      <c r="G12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
+    <row r="13" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="G14" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="H14" s="18" t="s">
+      <c r="H14" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="19" t="s">
+    <row r="15" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="H15" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
+    <row r="16" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="9" t="s">
         <v>22</v>
       </c>
     </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A17" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B17" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A18" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B18" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A19" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B19" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A20" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B20" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A21" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B21" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A22" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B22" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A23" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B23" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A24" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B24" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A25" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B25" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A26" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B26" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A27" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B27" s="15">
+        <v>0.84097222222222223</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A28" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B28" s="15">
+        <v>0.84097222222222223</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A29" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B29" s="15">
+        <v>0.84097222222222223</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A30" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B30" s="15">
+        <v>0.84097222222222223</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A31" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B31" s="15">
+        <v>0.84097222222222223</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A32" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B32" s="15">
+        <v>0.84097222222222223</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A33" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B33" s="15">
+        <v>0.84097222222222223</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A34" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B34" s="15">
+        <v>0.84097222222222223</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A35" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B35" s="15">
+        <v>0.84097222222222223</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A36" s="14">
+        <v>46206</v>
+      </c>
+      <c r="B36" s="15">
+        <v>0.84097222222222223</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A37" s="18">
+        <v>46206</v>
+      </c>
+      <c r="B37" s="19">
+        <v>0.87777777777777777</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A38" s="18">
+        <v>46206</v>
+      </c>
+      <c r="B38" s="19">
+        <v>0.87777777777777777</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A39" s="18">
+        <v>46206</v>
+      </c>
+      <c r="B39" s="19">
+        <v>0.87777777777777777</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A40" s="18">
+        <v>46206</v>
+      </c>
+      <c r="B40" s="19">
+        <v>0.87777777777777777</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G40" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A41" s="18">
+        <v>46206</v>
+      </c>
+      <c r="B41" s="19">
+        <v>0.87777777777777777</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="H41" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A42" s="18">
+        <v>46206</v>
+      </c>
+      <c r="B42" s="19">
+        <v>0.87777777777777777</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="G42" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="H42" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A43" s="18">
+        <v>46206</v>
+      </c>
+      <c r="B43" s="19">
+        <v>0.87777777777777777</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="H43" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A44" s="18">
+        <v>46206</v>
+      </c>
+      <c r="B44" s="19">
+        <v>0.87777777777777777</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D44" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="G44" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="H44" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A45" s="18">
+        <v>46206</v>
+      </c>
+      <c r="B45" s="19">
+        <v>0.87777777777777777</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="D45" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="F45" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="G45" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="H45" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A46" s="18">
+        <v>46206</v>
+      </c>
+      <c r="B46" s="19">
+        <v>0.87777777777777777</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="G46" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="H46" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="14.25" customHeight="1"/>
+    <row r="48" spans="1:8" ht="14.25" customHeight="1"/>
+    <row r="49" ht="14.25" customHeight="1"/>
+    <row r="50" ht="14.25" customHeight="1"/>
+    <row r="51" ht="14.25" customHeight="1"/>
+    <row r="52" ht="14.25" customHeight="1"/>
+    <row r="53" ht="14.25" customHeight="1"/>
+    <row r="54" ht="14.25" customHeight="1"/>
+    <row r="55" ht="14.25" customHeight="1"/>
+    <row r="56" ht="14.25" customHeight="1"/>
+    <row r="57" ht="14.25" customHeight="1"/>
+    <row r="58" ht="14.25" customHeight="1"/>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
+    <row r="74" ht="14.25" customHeight="1"/>
+    <row r="75" ht="14.25" customHeight="1"/>
+    <row r="76" ht="14.25" customHeight="1"/>
+    <row r="77" ht="14.25" customHeight="1"/>
+    <row r="78" ht="14.25" customHeight="1"/>
+    <row r="79" ht="14.25" customHeight="1"/>
+    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="81" ht="14.25" customHeight="1"/>
+    <row r="82" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1"/>
+    <row r="85" ht="14.25" customHeight="1"/>
+    <row r="86" ht="14.25" customHeight="1"/>
+    <row r="87" ht="14.25" customHeight="1"/>
+    <row r="88" ht="14.25" customHeight="1"/>
+    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
+    <row r="95" ht="14.25" customHeight="1"/>
+    <row r="96" ht="14.25" customHeight="1"/>
+    <row r="97" ht="14.25" customHeight="1"/>
+    <row r="98" ht="14.25" customHeight="1"/>
+    <row r="99" ht="14.25" customHeight="1"/>
+    <row r="100" ht="14.25" customHeight="1"/>
+    <row r="101" ht="14.25" customHeight="1"/>
+    <row r="102" ht="14.25" customHeight="1"/>
+    <row r="103" ht="14.25" customHeight="1"/>
+    <row r="104" ht="14.25" customHeight="1"/>
+    <row r="105" ht="14.25" customHeight="1"/>
+    <row r="106" ht="14.25" customHeight="1"/>
+    <row r="107" ht="14.25" customHeight="1"/>
+    <row r="108" ht="14.25" customHeight="1"/>
+    <row r="109" ht="14.25" customHeight="1"/>
+    <row r="110" ht="14.25" customHeight="1"/>
+    <row r="111" ht="14.25" customHeight="1"/>
+    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="113" ht="14.25" customHeight="1"/>
+    <row r="114" ht="14.25" customHeight="1"/>
+    <row r="115" ht="14.25" customHeight="1"/>
+    <row r="116" ht="14.25" customHeight="1"/>
+    <row r="117" ht="14.25" customHeight="1"/>
+    <row r="118" ht="14.25" customHeight="1"/>
+    <row r="119" ht="14.25" customHeight="1"/>
+    <row r="120" ht="14.25" customHeight="1"/>
+    <row r="121" ht="14.25" customHeight="1"/>
+    <row r="122" ht="14.25" customHeight="1"/>
+    <row r="123" ht="14.25" customHeight="1"/>
+    <row r="124" ht="14.25" customHeight="1"/>
+    <row r="125" ht="14.25" customHeight="1"/>
+    <row r="126" ht="14.25" customHeight="1"/>
+    <row r="127" ht="14.25" customHeight="1"/>
+    <row r="128" ht="14.25" customHeight="1"/>
+    <row r="129" ht="14.25" customHeight="1"/>
+    <row r="130" ht="14.25" customHeight="1"/>
+    <row r="131" ht="14.25" customHeight="1"/>
+    <row r="132" ht="14.25" customHeight="1"/>
+    <row r="133" ht="14.25" customHeight="1"/>
+    <row r="134" ht="14.25" customHeight="1"/>
+    <row r="135" ht="14.25" customHeight="1"/>
+    <row r="136" ht="14.25" customHeight="1"/>
+    <row r="137" ht="14.25" customHeight="1"/>
+    <row r="138" ht="14.25" customHeight="1"/>
+    <row r="139" ht="14.25" customHeight="1"/>
+    <row r="140" ht="14.25" customHeight="1"/>
+    <row r="141" ht="14.25" customHeight="1"/>
+    <row r="142" ht="14.25" customHeight="1"/>
+    <row r="143" ht="14.25" customHeight="1"/>
+    <row r="144" ht="14.25" customHeight="1"/>
+    <row r="145" ht="14.25" customHeight="1"/>
+    <row r="146" ht="14.25" customHeight="1"/>
+    <row r="147" ht="14.25" customHeight="1"/>
+    <row r="148" ht="14.25" customHeight="1"/>
+    <row r="149" ht="14.25" customHeight="1"/>
+    <row r="150" ht="14.25" customHeight="1"/>
+    <row r="151" ht="14.25" customHeight="1"/>
+    <row r="152" ht="14.25" customHeight="1"/>
+    <row r="153" ht="14.25" customHeight="1"/>
+    <row r="154" ht="14.25" customHeight="1"/>
+    <row r="155" ht="14.25" customHeight="1"/>
+    <row r="156" ht="14.25" customHeight="1"/>
+    <row r="157" ht="14.25" customHeight="1"/>
+    <row r="158" ht="14.25" customHeight="1"/>
+    <row r="159" ht="14.25" customHeight="1"/>
+    <row r="160" ht="14.25" customHeight="1"/>
+    <row r="161" ht="14.25" customHeight="1"/>
+    <row r="162" ht="14.25" customHeight="1"/>
+    <row r="163" ht="14.25" customHeight="1"/>
+    <row r="164" ht="14.25" customHeight="1"/>
+    <row r="165" ht="14.25" customHeight="1"/>
+    <row r="166" ht="14.25" customHeight="1"/>
+    <row r="167" ht="14.25" customHeight="1"/>
+    <row r="168" ht="14.25" customHeight="1"/>
+    <row r="169" ht="14.25" customHeight="1"/>
+    <row r="170" ht="14.25" customHeight="1"/>
+    <row r="171" ht="14.25" customHeight="1"/>
+    <row r="172" ht="14.25" customHeight="1"/>
+    <row r="173" ht="14.25" customHeight="1"/>
+    <row r="174" ht="14.25" customHeight="1"/>
+    <row r="175" ht="14.25" customHeight="1"/>
+    <row r="176" ht="14.25" customHeight="1"/>
+    <row r="177" ht="14.25" customHeight="1"/>
+    <row r="178" ht="14.25" customHeight="1"/>
+    <row r="179" ht="14.25" customHeight="1"/>
+    <row r="180" ht="14.25" customHeight="1"/>
+    <row r="181" ht="14.25" customHeight="1"/>
+    <row r="182" ht="14.25" customHeight="1"/>
+    <row r="183" ht="14.25" customHeight="1"/>
+    <row r="184" ht="14.25" customHeight="1"/>
+    <row r="185" ht="14.25" customHeight="1"/>
+    <row r="186" ht="14.25" customHeight="1"/>
+    <row r="187" ht="14.25" customHeight="1"/>
+    <row r="188" ht="14.25" customHeight="1"/>
+    <row r="189" ht="14.25" customHeight="1"/>
+    <row r="190" ht="14.25" customHeight="1"/>
+    <row r="191" ht="14.25" customHeight="1"/>
+    <row r="192" ht="14.25" customHeight="1"/>
+    <row r="193" ht="14.25" customHeight="1"/>
+    <row r="194" ht="14.25" customHeight="1"/>
+    <row r="195" ht="14.25" customHeight="1"/>
+    <row r="196" ht="14.25" customHeight="1"/>
+    <row r="197" ht="14.25" customHeight="1"/>
+    <row r="198" ht="14.25" customHeight="1"/>
+    <row r="199" ht="14.25" customHeight="1"/>
+    <row r="200" ht="14.25" customHeight="1"/>
+    <row r="201" ht="14.25" customHeight="1"/>
+    <row r="202" ht="14.25" customHeight="1"/>
+    <row r="203" ht="14.25" customHeight="1"/>
+    <row r="204" ht="14.25" customHeight="1"/>
+    <row r="205" ht="14.25" customHeight="1"/>
+    <row r="206" ht="14.25" customHeight="1"/>
+    <row r="207" ht="14.25" customHeight="1"/>
+    <row r="208" ht="14.25" customHeight="1"/>
+    <row r="209" ht="14.25" customHeight="1"/>
+    <row r="210" ht="14.25" customHeight="1"/>
+    <row r="211" ht="14.25" customHeight="1"/>
+    <row r="212" ht="14.25" customHeight="1"/>
+    <row r="213" ht="14.25" customHeight="1"/>
+    <row r="214" ht="14.25" customHeight="1"/>
+    <row r="215" ht="14.25" customHeight="1"/>
+    <row r="216" ht="14.25" customHeight="1"/>
+    <row r="217" ht="14.25" customHeight="1"/>
+    <row r="218" ht="14.25" customHeight="1"/>
+    <row r="219" ht="14.25" customHeight="1"/>
+    <row r="220" ht="14.25" customHeight="1"/>
+    <row r="221" ht="14.25" customHeight="1"/>
+    <row r="222" ht="14.25" customHeight="1"/>
+    <row r="223" ht="14.25" customHeight="1"/>
+    <row r="224" ht="14.25" customHeight="1"/>
+    <row r="225" ht="14.25" customHeight="1"/>
+    <row r="226" ht="14.25" customHeight="1"/>
+    <row r="227" ht="14.25" customHeight="1"/>
+    <row r="228" ht="14.25" customHeight="1"/>
+    <row r="229" ht="14.25" customHeight="1"/>
+    <row r="230" ht="14.25" customHeight="1"/>
+    <row r="231" ht="14.25" customHeight="1"/>
+    <row r="232" ht="14.25" customHeight="1"/>
+    <row r="233" ht="14.25" customHeight="1"/>
+    <row r="234" ht="14.25" customHeight="1"/>
+    <row r="235" ht="14.25" customHeight="1"/>
+    <row r="236" ht="14.25" customHeight="1"/>
+    <row r="237" ht="14.25" customHeight="1"/>
+    <row r="238" ht="14.25" customHeight="1"/>
+    <row r="239" ht="14.25" customHeight="1"/>
+    <row r="240" ht="14.25" customHeight="1"/>
+    <row r="241" ht="14.25" customHeight="1"/>
+    <row r="242" ht="14.25" customHeight="1"/>
+    <row r="243" ht="14.25" customHeight="1"/>
+    <row r="244" ht="14.25" customHeight="1"/>
+    <row r="245" ht="14.25" customHeight="1"/>
+    <row r="246" ht="14.25" customHeight="1"/>
+    <row r="247" ht="14.25" customHeight="1"/>
+    <row r="248" ht="14.25" customHeight="1"/>
+    <row r="249" ht="14.25" customHeight="1"/>
+    <row r="250" ht="14.25" customHeight="1"/>
+    <row r="251" ht="14.25" customHeight="1"/>
+    <row r="252" ht="14.25" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
+    <row r="254" ht="14.25" customHeight="1"/>
+    <row r="255" ht="14.25" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
+    <row r="257" ht="14.25" customHeight="1"/>
+    <row r="258" ht="14.25" customHeight="1"/>
+    <row r="259" ht="14.25" customHeight="1"/>
+    <row r="260" ht="14.25" customHeight="1"/>
+    <row r="261" ht="14.25" customHeight="1"/>
+    <row r="262" ht="14.25" customHeight="1"/>
+    <row r="263" ht="14.25" customHeight="1"/>
+    <row r="264" ht="14.25" customHeight="1"/>
+    <row r="265" ht="14.25" customHeight="1"/>
+    <row r="266" ht="14.25" customHeight="1"/>
+    <row r="267" ht="14.25" customHeight="1"/>
+    <row r="268" ht="14.25" customHeight="1"/>
+    <row r="269" ht="14.25" customHeight="1"/>
+    <row r="270" ht="14.25" customHeight="1"/>
+    <row r="271" ht="14.25" customHeight="1"/>
+    <row r="272" ht="14.25" customHeight="1"/>
+    <row r="273" ht="14.25" customHeight="1"/>
+    <row r="274" ht="14.25" customHeight="1"/>
+    <row r="275" ht="14.25" customHeight="1"/>
+    <row r="276" ht="14.25" customHeight="1"/>
+    <row r="277" ht="14.25" customHeight="1"/>
+    <row r="278" ht="14.25" customHeight="1"/>
+    <row r="279" ht="14.25" customHeight="1"/>
+    <row r="280" ht="14.25" customHeight="1"/>
+    <row r="281" ht="14.25" customHeight="1"/>
+    <row r="282" ht="14.25" customHeight="1"/>
+    <row r="283" ht="14.25" customHeight="1"/>
+    <row r="284" ht="14.25" customHeight="1"/>
+    <row r="285" ht="14.25" customHeight="1"/>
+    <row r="286" ht="14.25" customHeight="1"/>
+    <row r="287" ht="14.25" customHeight="1"/>
+    <row r="288" ht="14.25" customHeight="1"/>
+    <row r="289" ht="14.25" customHeight="1"/>
+    <row r="290" ht="14.25" customHeight="1"/>
+    <row r="291" ht="14.25" customHeight="1"/>
+    <row r="292" ht="14.25" customHeight="1"/>
+    <row r="293" ht="14.25" customHeight="1"/>
+    <row r="294" ht="14.25" customHeight="1"/>
+    <row r="295" ht="14.25" customHeight="1"/>
+    <row r="296" ht="14.25" customHeight="1"/>
+    <row r="297" ht="14.25" customHeight="1"/>
+    <row r="298" ht="14.25" customHeight="1"/>
+    <row r="299" ht="14.25" customHeight="1"/>
+    <row r="300" ht="14.25" customHeight="1"/>
+    <row r="301" ht="14.25" customHeight="1"/>
+    <row r="302" ht="14.25" customHeight="1"/>
+    <row r="303" ht="14.25" customHeight="1"/>
+    <row r="304" ht="14.25" customHeight="1"/>
+    <row r="305" ht="14.25" customHeight="1"/>
+    <row r="306" ht="14.25" customHeight="1"/>
+    <row r="307" ht="14.25" customHeight="1"/>
+    <row r="308" ht="14.25" customHeight="1"/>
+    <row r="309" ht="14.25" customHeight="1"/>
+    <row r="310" ht="14.25" customHeight="1"/>
+    <row r="311" ht="14.25" customHeight="1"/>
+    <row r="312" ht="14.25" customHeight="1"/>
+    <row r="313" ht="14.25" customHeight="1"/>
+    <row r="314" ht="14.25" customHeight="1"/>
+    <row r="315" ht="14.25" customHeight="1"/>
+    <row r="316" ht="14.25" customHeight="1"/>
+    <row r="317" ht="14.25" customHeight="1"/>
+    <row r="318" ht="14.25" customHeight="1"/>
+    <row r="319" ht="14.25" customHeight="1"/>
+    <row r="320" ht="14.25" customHeight="1"/>
+    <row r="321" ht="14.25" customHeight="1"/>
+    <row r="322" ht="14.25" customHeight="1"/>
+    <row r="323" ht="14.25" customHeight="1"/>
+    <row r="324" ht="14.25" customHeight="1"/>
+    <row r="325" ht="14.25" customHeight="1"/>
+    <row r="326" ht="14.25" customHeight="1"/>
+    <row r="327" ht="14.25" customHeight="1"/>
+    <row r="328" ht="14.25" customHeight="1"/>
+    <row r="329" ht="14.25" customHeight="1"/>
+    <row r="330" ht="14.25" customHeight="1"/>
+    <row r="331" ht="14.25" customHeight="1"/>
+    <row r="332" ht="14.25" customHeight="1"/>
+    <row r="333" ht="14.25" customHeight="1"/>
+    <row r="334" ht="14.25" customHeight="1"/>
+    <row r="335" ht="14.25" customHeight="1"/>
+    <row r="336" ht="14.25" customHeight="1"/>
+    <row r="337" ht="14.25" customHeight="1"/>
+    <row r="338" ht="14.25" customHeight="1"/>
+    <row r="339" ht="14.25" customHeight="1"/>
+    <row r="340" ht="14.25" customHeight="1"/>
+    <row r="341" ht="14.25" customHeight="1"/>
+    <row r="342" ht="14.25" customHeight="1"/>
+    <row r="343" ht="14.25" customHeight="1"/>
+    <row r="344" ht="14.25" customHeight="1"/>
+    <row r="345" ht="14.25" customHeight="1"/>
+    <row r="346" ht="14.25" customHeight="1"/>
+    <row r="347" ht="14.25" customHeight="1"/>
+    <row r="348" ht="14.25" customHeight="1"/>
+    <row r="349" ht="14.25" customHeight="1"/>
+    <row r="350" ht="14.25" customHeight="1"/>
+    <row r="351" ht="14.25" customHeight="1"/>
+    <row r="352" ht="14.25" customHeight="1"/>
+    <row r="353" ht="14.25" customHeight="1"/>
+    <row r="354" ht="14.25" customHeight="1"/>
+    <row r="355" ht="14.25" customHeight="1"/>
+    <row r="356" ht="14.25" customHeight="1"/>
+    <row r="357" ht="14.25" customHeight="1"/>
+    <row r="358" ht="14.25" customHeight="1"/>
+    <row r="359" ht="14.25" customHeight="1"/>
+    <row r="360" ht="14.25" customHeight="1"/>
+    <row r="361" ht="14.25" customHeight="1"/>
+    <row r="362" ht="14.25" customHeight="1"/>
+    <row r="363" ht="14.25" customHeight="1"/>
+    <row r="364" ht="14.25" customHeight="1"/>
+    <row r="365" ht="14.25" customHeight="1"/>
+    <row r="366" ht="14.25" customHeight="1"/>
+    <row r="367" ht="14.25" customHeight="1"/>
+    <row r="368" ht="14.25" customHeight="1"/>
+    <row r="369" ht="14.25" customHeight="1"/>
+    <row r="370" ht="14.25" customHeight="1"/>
+    <row r="371" ht="14.25" customHeight="1"/>
+    <row r="372" ht="14.25" customHeight="1"/>
+    <row r="373" ht="14.25" customHeight="1"/>
+    <row r="374" ht="14.25" customHeight="1"/>
+    <row r="375" ht="14.25" customHeight="1"/>
+    <row r="376" ht="14.25" customHeight="1"/>
+    <row r="377" ht="14.25" customHeight="1"/>
+    <row r="378" ht="14.25" customHeight="1"/>
+    <row r="379" ht="14.25" customHeight="1"/>
+    <row r="380" ht="14.25" customHeight="1"/>
+    <row r="381" ht="14.25" customHeight="1"/>
+    <row r="382" ht="14.25" customHeight="1"/>
+    <row r="383" ht="14.25" customHeight="1"/>
+    <row r="384" ht="14.25" customHeight="1"/>
+    <row r="385" ht="14.25" customHeight="1"/>
+    <row r="386" ht="14.25" customHeight="1"/>
+    <row r="387" ht="14.25" customHeight="1"/>
+    <row r="388" ht="14.25" customHeight="1"/>
+    <row r="389" ht="14.25" customHeight="1"/>
+    <row r="390" ht="14.25" customHeight="1"/>
+    <row r="391" ht="14.25" customHeight="1"/>
+    <row r="392" ht="14.25" customHeight="1"/>
+    <row r="393" ht="14.25" customHeight="1"/>
+    <row r="394" ht="14.25" customHeight="1"/>
+    <row r="395" ht="14.25" customHeight="1"/>
+    <row r="396" ht="14.25" customHeight="1"/>
+    <row r="397" ht="14.25" customHeight="1"/>
+    <row r="398" ht="14.25" customHeight="1"/>
+    <row r="399" ht="14.25" customHeight="1"/>
+    <row r="400" ht="14.25" customHeight="1"/>
+    <row r="401" ht="14.25" customHeight="1"/>
+    <row r="402" ht="14.25" customHeight="1"/>
+    <row r="403" ht="14.25" customHeight="1"/>
+    <row r="404" ht="14.25" customHeight="1"/>
+    <row r="405" ht="14.25" customHeight="1"/>
+    <row r="406" ht="14.25" customHeight="1"/>
+    <row r="407" ht="14.25" customHeight="1"/>
+    <row r="408" ht="14.25" customHeight="1"/>
+    <row r="409" ht="14.25" customHeight="1"/>
+    <row r="410" ht="14.25" customHeight="1"/>
+    <row r="411" ht="14.25" customHeight="1"/>
+    <row r="412" ht="14.25" customHeight="1"/>
+    <row r="413" ht="14.25" customHeight="1"/>
+    <row r="414" ht="14.25" customHeight="1"/>
+    <row r="415" ht="14.25" customHeight="1"/>
+    <row r="416" ht="14.25" customHeight="1"/>
+    <row r="417" ht="14.25" customHeight="1"/>
+    <row r="418" ht="14.25" customHeight="1"/>
+    <row r="419" ht="14.25" customHeight="1"/>
+    <row r="420" ht="14.25" customHeight="1"/>
+    <row r="421" ht="14.25" customHeight="1"/>
+    <row r="422" ht="14.25" customHeight="1"/>
+    <row r="423" ht="14.25" customHeight="1"/>
+    <row r="424" ht="14.25" customHeight="1"/>
+    <row r="425" ht="14.25" customHeight="1"/>
+    <row r="426" ht="14.25" customHeight="1"/>
+    <row r="427" ht="14.25" customHeight="1"/>
+    <row r="428" ht="14.25" customHeight="1"/>
+    <row r="429" ht="14.25" customHeight="1"/>
+    <row r="430" ht="14.25" customHeight="1"/>
+    <row r="431" ht="14.25" customHeight="1"/>
+    <row r="432" ht="14.25" customHeight="1"/>
+    <row r="433" ht="14.25" customHeight="1"/>
+    <row r="434" ht="14.25" customHeight="1"/>
+    <row r="435" ht="14.25" customHeight="1"/>
+    <row r="436" ht="14.25" customHeight="1"/>
+    <row r="437" ht="14.25" customHeight="1"/>
+    <row r="438" ht="14.25" customHeight="1"/>
+    <row r="439" ht="14.25" customHeight="1"/>
+    <row r="440" ht="14.25" customHeight="1"/>
+    <row r="441" ht="14.25" customHeight="1"/>
+    <row r="442" ht="14.25" customHeight="1"/>
+    <row r="443" ht="14.25" customHeight="1"/>
+    <row r="444" ht="14.25" customHeight="1"/>
+    <row r="445" ht="14.25" customHeight="1"/>
+    <row r="446" ht="14.25" customHeight="1"/>
+    <row r="447" ht="14.25" customHeight="1"/>
+    <row r="448" ht="14.25" customHeight="1"/>
+    <row r="449" ht="14.25" customHeight="1"/>
+    <row r="450" ht="14.25" customHeight="1"/>
+    <row r="451" ht="14.25" customHeight="1"/>
+    <row r="452" ht="14.25" customHeight="1"/>
+    <row r="453" ht="14.25" customHeight="1"/>
+    <row r="454" ht="14.25" customHeight="1"/>
+    <row r="455" ht="14.25" customHeight="1"/>
+    <row r="456" ht="14.25" customHeight="1"/>
+    <row r="457" ht="14.25" customHeight="1"/>
+    <row r="458" ht="14.25" customHeight="1"/>
+    <row r="459" ht="14.25" customHeight="1"/>
+    <row r="460" ht="14.25" customHeight="1"/>
+    <row r="461" ht="14.25" customHeight="1"/>
+    <row r="462" ht="14.25" customHeight="1"/>
+    <row r="463" ht="14.25" customHeight="1"/>
+    <row r="464" ht="14.25" customHeight="1"/>
+    <row r="465" ht="14.25" customHeight="1"/>
+    <row r="466" ht="14.25" customHeight="1"/>
+    <row r="467" ht="14.25" customHeight="1"/>
+    <row r="468" ht="14.25" customHeight="1"/>
+    <row r="469" ht="14.25" customHeight="1"/>
+    <row r="470" ht="14.25" customHeight="1"/>
+    <row r="471" ht="14.25" customHeight="1"/>
+    <row r="472" ht="14.25" customHeight="1"/>
+    <row r="473" ht="14.25" customHeight="1"/>
+    <row r="474" ht="14.25" customHeight="1"/>
+    <row r="475" ht="14.25" customHeight="1"/>
+    <row r="476" ht="14.25" customHeight="1"/>
+    <row r="477" ht="14.25" customHeight="1"/>
+    <row r="478" ht="14.25" customHeight="1"/>
+    <row r="479" ht="14.25" customHeight="1"/>
+    <row r="480" ht="14.25" customHeight="1"/>
+    <row r="481" ht="14.25" customHeight="1"/>
+    <row r="482" ht="14.25" customHeight="1"/>
+    <row r="483" ht="14.25" customHeight="1"/>
+    <row r="484" ht="14.25" customHeight="1"/>
+    <row r="485" ht="14.25" customHeight="1"/>
+    <row r="486" ht="14.25" customHeight="1"/>
+    <row r="487" ht="14.25" customHeight="1"/>
+    <row r="488" ht="14.25" customHeight="1"/>
+    <row r="489" ht="14.25" customHeight="1"/>
+    <row r="490" ht="14.25" customHeight="1"/>
+    <row r="491" ht="14.25" customHeight="1"/>
+    <row r="492" ht="14.25" customHeight="1"/>
+    <row r="493" ht="14.25" customHeight="1"/>
+    <row r="494" ht="14.25" customHeight="1"/>
+    <row r="495" ht="14.25" customHeight="1"/>
+    <row r="496" ht="14.25" customHeight="1"/>
+    <row r="497" ht="14.25" customHeight="1"/>
+    <row r="498" ht="14.25" customHeight="1"/>
+    <row r="499" ht="14.25" customHeight="1"/>
+    <row r="500" ht="14.25" customHeight="1"/>
+    <row r="501" ht="14.25" customHeight="1"/>
+    <row r="502" ht="14.25" customHeight="1"/>
+    <row r="503" ht="14.25" customHeight="1"/>
+    <row r="504" ht="14.25" customHeight="1"/>
+    <row r="505" ht="14.25" customHeight="1"/>
+    <row r="506" ht="14.25" customHeight="1"/>
+    <row r="507" ht="14.25" customHeight="1"/>
+    <row r="508" ht="14.25" customHeight="1"/>
+    <row r="509" ht="14.25" customHeight="1"/>
+    <row r="510" ht="14.25" customHeight="1"/>
+    <row r="511" ht="14.25" customHeight="1"/>
+    <row r="512" ht="14.25" customHeight="1"/>
+    <row r="513" ht="14.25" customHeight="1"/>
+    <row r="514" ht="14.25" customHeight="1"/>
+    <row r="515" ht="14.25" customHeight="1"/>
+    <row r="516" ht="14.25" customHeight="1"/>
+    <row r="517" ht="14.25" customHeight="1"/>
+    <row r="518" ht="14.25" customHeight="1"/>
+    <row r="519" ht="14.25" customHeight="1"/>
+    <row r="520" ht="14.25" customHeight="1"/>
+    <row r="521" ht="14.25" customHeight="1"/>
+    <row r="522" ht="14.25" customHeight="1"/>
+    <row r="523" ht="14.25" customHeight="1"/>
+    <row r="524" ht="14.25" customHeight="1"/>
+    <row r="525" ht="14.25" customHeight="1"/>
+    <row r="526" ht="14.25" customHeight="1"/>
+    <row r="527" ht="14.25" customHeight="1"/>
+    <row r="528" ht="14.25" customHeight="1"/>
+    <row r="529" ht="14.25" customHeight="1"/>
+    <row r="530" ht="14.25" customHeight="1"/>
+    <row r="531" ht="14.25" customHeight="1"/>
+    <row r="532" ht="14.25" customHeight="1"/>
+    <row r="533" ht="14.25" customHeight="1"/>
+    <row r="534" ht="14.25" customHeight="1"/>
+    <row r="535" ht="14.25" customHeight="1"/>
+    <row r="536" ht="14.25" customHeight="1"/>
+    <row r="537" ht="14.25" customHeight="1"/>
+    <row r="538" ht="14.25" customHeight="1"/>
+    <row r="539" ht="14.25" customHeight="1"/>
+    <row r="540" ht="14.25" customHeight="1"/>
+    <row r="541" ht="14.25" customHeight="1"/>
+    <row r="542" ht="14.25" customHeight="1"/>
+    <row r="543" ht="14.25" customHeight="1"/>
+    <row r="544" ht="14.25" customHeight="1"/>
+    <row r="545" ht="14.25" customHeight="1"/>
+    <row r="546" ht="14.25" customHeight="1"/>
+    <row r="547" ht="14.25" customHeight="1"/>
+    <row r="548" ht="14.25" customHeight="1"/>
+    <row r="549" ht="14.25" customHeight="1"/>
+    <row r="550" ht="14.25" customHeight="1"/>
+    <row r="551" ht="14.25" customHeight="1"/>
+    <row r="552" ht="14.25" customHeight="1"/>
+    <row r="553" ht="14.25" customHeight="1"/>
+    <row r="554" ht="14.25" customHeight="1"/>
+    <row r="555" ht="14.25" customHeight="1"/>
+    <row r="556" ht="14.25" customHeight="1"/>
+    <row r="557" ht="14.25" customHeight="1"/>
+    <row r="558" ht="14.25" customHeight="1"/>
+    <row r="559" ht="14.25" customHeight="1"/>
+    <row r="560" ht="14.25" customHeight="1"/>
+    <row r="561" ht="14.25" customHeight="1"/>
+    <row r="562" ht="14.25" customHeight="1"/>
+    <row r="563" ht="14.25" customHeight="1"/>
+    <row r="564" ht="14.25" customHeight="1"/>
+    <row r="565" ht="14.25" customHeight="1"/>
+    <row r="566" ht="14.25" customHeight="1"/>
+    <row r="567" ht="14.25" customHeight="1"/>
+    <row r="568" ht="14.25" customHeight="1"/>
+    <row r="569" ht="14.25" customHeight="1"/>
+    <row r="570" ht="14.25" customHeight="1"/>
+    <row r="571" ht="14.25" customHeight="1"/>
+    <row r="572" ht="14.25" customHeight="1"/>
+    <row r="573" ht="14.25" customHeight="1"/>
+    <row r="574" ht="14.25" customHeight="1"/>
+    <row r="575" ht="14.25" customHeight="1"/>
+    <row r="576" ht="14.25" customHeight="1"/>
+    <row r="577" ht="14.25" customHeight="1"/>
+    <row r="578" ht="14.25" customHeight="1"/>
+    <row r="579" ht="14.25" customHeight="1"/>
+    <row r="580" ht="14.25" customHeight="1"/>
+    <row r="581" ht="14.25" customHeight="1"/>
+    <row r="582" ht="14.25" customHeight="1"/>
+    <row r="583" ht="14.25" customHeight="1"/>
+    <row r="584" ht="14.25" customHeight="1"/>
+    <row r="585" ht="14.25" customHeight="1"/>
+    <row r="586" ht="14.25" customHeight="1"/>
+    <row r="587" ht="14.25" customHeight="1"/>
+    <row r="588" ht="14.25" customHeight="1"/>
+    <row r="589" ht="14.25" customHeight="1"/>
+    <row r="590" ht="14.25" customHeight="1"/>
+    <row r="591" ht="14.25" customHeight="1"/>
+    <row r="592" ht="14.25" customHeight="1"/>
+    <row r="593" ht="14.25" customHeight="1"/>
+    <row r="594" ht="14.25" customHeight="1"/>
+    <row r="595" ht="14.25" customHeight="1"/>
+    <row r="596" ht="14.25" customHeight="1"/>
+    <row r="597" ht="14.25" customHeight="1"/>
+    <row r="598" ht="14.25" customHeight="1"/>
+    <row r="599" ht="14.25" customHeight="1"/>
+    <row r="600" ht="14.25" customHeight="1"/>
+    <row r="601" ht="14.25" customHeight="1"/>
+    <row r="602" ht="14.25" customHeight="1"/>
+    <row r="603" ht="14.25" customHeight="1"/>
+    <row r="604" ht="14.25" customHeight="1"/>
+    <row r="605" ht="14.25" customHeight="1"/>
+    <row r="606" ht="14.25" customHeight="1"/>
+    <row r="607" ht="14.25" customHeight="1"/>
+    <row r="608" ht="14.25" customHeight="1"/>
+    <row r="609" ht="14.25" customHeight="1"/>
+    <row r="610" ht="14.25" customHeight="1"/>
+    <row r="611" ht="14.25" customHeight="1"/>
+    <row r="612" ht="14.25" customHeight="1"/>
+    <row r="613" ht="14.25" customHeight="1"/>
+    <row r="614" ht="14.25" customHeight="1"/>
+    <row r="615" ht="14.25" customHeight="1"/>
+    <row r="616" ht="14.25" customHeight="1"/>
+    <row r="617" ht="14.25" customHeight="1"/>
+    <row r="618" ht="14.25" customHeight="1"/>
+    <row r="619" ht="14.25" customHeight="1"/>
+    <row r="620" ht="14.25" customHeight="1"/>
+    <row r="621" ht="14.25" customHeight="1"/>
+    <row r="622" ht="14.25" customHeight="1"/>
+    <row r="623" ht="14.25" customHeight="1"/>
+    <row r="624" ht="14.25" customHeight="1"/>
+    <row r="625" ht="14.25" customHeight="1"/>
+    <row r="626" ht="14.25" customHeight="1"/>
+    <row r="627" ht="14.25" customHeight="1"/>
+    <row r="628" ht="14.25" customHeight="1"/>
+    <row r="629" ht="14.25" customHeight="1"/>
+    <row r="630" ht="14.25" customHeight="1"/>
+    <row r="631" ht="14.25" customHeight="1"/>
+    <row r="632" ht="14.25" customHeight="1"/>
+    <row r="633" ht="14.25" customHeight="1"/>
+    <row r="634" ht="14.25" customHeight="1"/>
+    <row r="635" ht="14.25" customHeight="1"/>
+    <row r="636" ht="14.25" customHeight="1"/>
+    <row r="637" ht="14.25" customHeight="1"/>
+    <row r="638" ht="14.25" customHeight="1"/>
+    <row r="639" ht="14.25" customHeight="1"/>
+    <row r="640" ht="14.25" customHeight="1"/>
+    <row r="641" ht="14.25" customHeight="1"/>
+    <row r="642" ht="14.25" customHeight="1"/>
+    <row r="643" ht="14.25" customHeight="1"/>
+    <row r="644" ht="14.25" customHeight="1"/>
+    <row r="645" ht="14.25" customHeight="1"/>
+    <row r="646" ht="14.25" customHeight="1"/>
+    <row r="647" ht="14.25" customHeight="1"/>
+    <row r="648" ht="14.25" customHeight="1"/>
+    <row r="649" ht="14.25" customHeight="1"/>
+    <row r="650" ht="14.25" customHeight="1"/>
+    <row r="651" ht="14.25" customHeight="1"/>
+    <row r="652" ht="14.25" customHeight="1"/>
+    <row r="653" ht="14.25" customHeight="1"/>
+    <row r="654" ht="14.25" customHeight="1"/>
+    <row r="655" ht="14.25" customHeight="1"/>
+    <row r="656" ht="14.25" customHeight="1"/>
+    <row r="657" ht="14.25" customHeight="1"/>
+    <row r="658" ht="14.25" customHeight="1"/>
+    <row r="659" ht="14.25" customHeight="1"/>
+    <row r="660" ht="14.25" customHeight="1"/>
+    <row r="661" ht="14.25" customHeight="1"/>
+    <row r="662" ht="14.25" customHeight="1"/>
+    <row r="663" ht="14.25" customHeight="1"/>
+    <row r="664" ht="14.25" customHeight="1"/>
+    <row r="665" ht="14.25" customHeight="1"/>
+    <row r="666" ht="14.25" customHeight="1"/>
+    <row r="667" ht="14.25" customHeight="1"/>
+    <row r="668" ht="14.25" customHeight="1"/>
+    <row r="669" ht="14.25" customHeight="1"/>
+    <row r="670" ht="14.25" customHeight="1"/>
+    <row r="671" ht="14.25" customHeight="1"/>
+    <row r="672" ht="14.25" customHeight="1"/>
+    <row r="673" ht="14.25" customHeight="1"/>
+    <row r="674" ht="14.25" customHeight="1"/>
+    <row r="675" ht="14.25" customHeight="1"/>
+    <row r="676" ht="14.25" customHeight="1"/>
+    <row r="677" ht="14.25" customHeight="1"/>
+    <row r="678" ht="14.25" customHeight="1"/>
+    <row r="679" ht="14.25" customHeight="1"/>
+    <row r="680" ht="14.25" customHeight="1"/>
+    <row r="681" ht="14.25" customHeight="1"/>
+    <row r="682" ht="14.25" customHeight="1"/>
+    <row r="683" ht="14.25" customHeight="1"/>
+    <row r="684" ht="14.25" customHeight="1"/>
+    <row r="685" ht="14.25" customHeight="1"/>
+    <row r="686" ht="14.25" customHeight="1"/>
+    <row r="687" ht="14.25" customHeight="1"/>
+    <row r="688" ht="14.25" customHeight="1"/>
+    <row r="689" ht="14.25" customHeight="1"/>
+    <row r="690" ht="14.25" customHeight="1"/>
+    <row r="691" ht="14.25" customHeight="1"/>
+    <row r="692" ht="14.25" customHeight="1"/>
+    <row r="693" ht="14.25" customHeight="1"/>
+    <row r="694" ht="14.25" customHeight="1"/>
+    <row r="695" ht="14.25" customHeight="1"/>
+    <row r="696" ht="14.25" customHeight="1"/>
+    <row r="697" ht="14.25" customHeight="1"/>
+    <row r="698" ht="14.25" customHeight="1"/>
+    <row r="699" ht="14.25" customHeight="1"/>
+    <row r="700" ht="14.25" customHeight="1"/>
+    <row r="701" ht="14.25" customHeight="1"/>
+    <row r="702" ht="14.25" customHeight="1"/>
+    <row r="703" ht="14.25" customHeight="1"/>
+    <row r="704" ht="14.25" customHeight="1"/>
+    <row r="705" ht="14.25" customHeight="1"/>
+    <row r="706" ht="14.25" customHeight="1"/>
+    <row r="707" ht="14.25" customHeight="1"/>
+    <row r="708" ht="14.25" customHeight="1"/>
+    <row r="709" ht="14.25" customHeight="1"/>
+    <row r="710" ht="14.25" customHeight="1"/>
+    <row r="711" ht="14.25" customHeight="1"/>
+    <row r="712" ht="14.25" customHeight="1"/>
+    <row r="713" ht="14.25" customHeight="1"/>
+    <row r="714" ht="14.25" customHeight="1"/>
+    <row r="715" ht="14.25" customHeight="1"/>
+    <row r="716" ht="14.25" customHeight="1"/>
+    <row r="717" ht="14.25" customHeight="1"/>
+    <row r="718" ht="14.25" customHeight="1"/>
+    <row r="719" ht="14.25" customHeight="1"/>
+    <row r="720" ht="14.25" customHeight="1"/>
+    <row r="721" ht="14.25" customHeight="1"/>
+    <row r="722" ht="14.25" customHeight="1"/>
+    <row r="723" ht="14.25" customHeight="1"/>
+    <row r="724" ht="14.25" customHeight="1"/>
+    <row r="725" ht="14.25" customHeight="1"/>
+    <row r="726" ht="14.25" customHeight="1"/>
+    <row r="727" ht="14.25" customHeight="1"/>
+    <row r="728" ht="14.25" customHeight="1"/>
+    <row r="729" ht="14.25" customHeight="1"/>
+    <row r="730" ht="14.25" customHeight="1"/>
+    <row r="731" ht="14.25" customHeight="1"/>
+    <row r="732" ht="14.25" customHeight="1"/>
+    <row r="733" ht="14.25" customHeight="1"/>
+    <row r="734" ht="14.25" customHeight="1"/>
+    <row r="735" ht="14.25" customHeight="1"/>
+    <row r="736" ht="14.25" customHeight="1"/>
+    <row r="737" ht="14.25" customHeight="1"/>
+    <row r="738" ht="14.25" customHeight="1"/>
+    <row r="739" ht="14.25" customHeight="1"/>
+    <row r="740" ht="14.25" customHeight="1"/>
+    <row r="741" ht="14.25" customHeight="1"/>
+    <row r="742" ht="14.25" customHeight="1"/>
+    <row r="743" ht="14.25" customHeight="1"/>
+    <row r="744" ht="14.25" customHeight="1"/>
+    <row r="745" ht="14.25" customHeight="1"/>
+    <row r="746" ht="14.25" customHeight="1"/>
+    <row r="747" ht="14.25" customHeight="1"/>
+    <row r="748" ht="14.25" customHeight="1"/>
+    <row r="749" ht="14.25" customHeight="1"/>
+    <row r="750" ht="14.25" customHeight="1"/>
+    <row r="751" ht="14.25" customHeight="1"/>
+    <row r="752" ht="14.25" customHeight="1"/>
+    <row r="753" ht="14.25" customHeight="1"/>
+    <row r="754" ht="14.25" customHeight="1"/>
+    <row r="755" ht="14.25" customHeight="1"/>
+    <row r="756" ht="14.25" customHeight="1"/>
+    <row r="757" ht="14.25" customHeight="1"/>
+    <row r="758" ht="14.25" customHeight="1"/>
+    <row r="759" ht="14.25" customHeight="1"/>
+    <row r="760" ht="14.25" customHeight="1"/>
+    <row r="761" ht="14.25" customHeight="1"/>
+    <row r="762" ht="14.25" customHeight="1"/>
+    <row r="763" ht="14.25" customHeight="1"/>
+    <row r="764" ht="14.25" customHeight="1"/>
+    <row r="765" ht="14.25" customHeight="1"/>
+    <row r="766" ht="14.25" customHeight="1"/>
+    <row r="767" ht="14.25" customHeight="1"/>
+    <row r="768" ht="14.25" customHeight="1"/>
+    <row r="769" ht="14.25" customHeight="1"/>
+    <row r="770" ht="14.25" customHeight="1"/>
+    <row r="771" ht="14.25" customHeight="1"/>
+    <row r="772" ht="14.25" customHeight="1"/>
+    <row r="773" ht="14.25" customHeight="1"/>
+    <row r="774" ht="14.25" customHeight="1"/>
+    <row r="775" ht="14.25" customHeight="1"/>
+    <row r="776" ht="14.25" customHeight="1"/>
+    <row r="777" ht="14.25" customHeight="1"/>
+    <row r="778" ht="14.25" customHeight="1"/>
+    <row r="779" ht="14.25" customHeight="1"/>
+    <row r="780" ht="14.25" customHeight="1"/>
+    <row r="781" ht="14.25" customHeight="1"/>
+    <row r="782" ht="14.25" customHeight="1"/>
+    <row r="783" ht="14.25" customHeight="1"/>
+    <row r="784" ht="14.25" customHeight="1"/>
+    <row r="785" ht="14.25" customHeight="1"/>
+    <row r="786" ht="14.25" customHeight="1"/>
+    <row r="787" ht="14.25" customHeight="1"/>
+    <row r="788" ht="14.25" customHeight="1"/>
+    <row r="789" ht="14.25" customHeight="1"/>
+    <row r="790" ht="14.25" customHeight="1"/>
+    <row r="791" ht="14.25" customHeight="1"/>
+    <row r="792" ht="14.25" customHeight="1"/>
+    <row r="793" ht="14.25" customHeight="1"/>
+    <row r="794" ht="14.25" customHeight="1"/>
+    <row r="795" ht="14.25" customHeight="1"/>
+    <row r="796" ht="14.25" customHeight="1"/>
+    <row r="797" ht="14.25" customHeight="1"/>
+    <row r="798" ht="14.25" customHeight="1"/>
+    <row r="799" ht="14.25" customHeight="1"/>
+    <row r="800" ht="14.25" customHeight="1"/>
+    <row r="801" ht="14.25" customHeight="1"/>
+    <row r="802" ht="14.25" customHeight="1"/>
+    <row r="803" ht="14.25" customHeight="1"/>
+    <row r="804" ht="14.25" customHeight="1"/>
+    <row r="805" ht="14.25" customHeight="1"/>
+    <row r="806" ht="14.25" customHeight="1"/>
+    <row r="807" ht="14.25" customHeight="1"/>
+    <row r="808" ht="14.25" customHeight="1"/>
+    <row r="809" ht="14.25" customHeight="1"/>
+    <row r="810" ht="14.25" customHeight="1"/>
+    <row r="811" ht="14.25" customHeight="1"/>
+    <row r="812" ht="14.25" customHeight="1"/>
+    <row r="813" ht="14.25" customHeight="1"/>
+    <row r="814" ht="14.25" customHeight="1"/>
+    <row r="815" ht="14.25" customHeight="1"/>
+    <row r="816" ht="14.25" customHeight="1"/>
+    <row r="817" ht="14.25" customHeight="1"/>
+    <row r="818" ht="14.25" customHeight="1"/>
+    <row r="819" ht="14.25" customHeight="1"/>
+    <row r="820" ht="14.25" customHeight="1"/>
+    <row r="821" ht="14.25" customHeight="1"/>
+    <row r="822" ht="14.25" customHeight="1"/>
+    <row r="823" ht="14.25" customHeight="1"/>
+    <row r="824" ht="14.25" customHeight="1"/>
+    <row r="825" ht="14.25" customHeight="1"/>
+    <row r="826" ht="14.25" customHeight="1"/>
+    <row r="827" ht="14.25" customHeight="1"/>
+    <row r="828" ht="14.25" customHeight="1"/>
+    <row r="829" ht="14.25" customHeight="1"/>
+    <row r="830" ht="14.25" customHeight="1"/>
+    <row r="831" ht="14.25" customHeight="1"/>
+    <row r="832" ht="14.25" customHeight="1"/>
+    <row r="833" ht="14.25" customHeight="1"/>
+    <row r="834" ht="14.25" customHeight="1"/>
+    <row r="835" ht="14.25" customHeight="1"/>
+    <row r="836" ht="14.25" customHeight="1"/>
+    <row r="837" ht="14.25" customHeight="1"/>
+    <row r="838" ht="14.25" customHeight="1"/>
+    <row r="839" ht="14.25" customHeight="1"/>
+    <row r="840" ht="14.25" customHeight="1"/>
+    <row r="841" ht="14.25" customHeight="1"/>
+    <row r="842" ht="14.25" customHeight="1"/>
+    <row r="843" ht="14.25" customHeight="1"/>
+    <row r="844" ht="14.25" customHeight="1"/>
+    <row r="845" ht="14.25" customHeight="1"/>
+    <row r="846" ht="14.25" customHeight="1"/>
+    <row r="847" ht="14.25" customHeight="1"/>
+    <row r="848" ht="14.25" customHeight="1"/>
+    <row r="849" ht="14.25" customHeight="1"/>
+    <row r="850" ht="14.25" customHeight="1"/>
+    <row r="851" ht="14.25" customHeight="1"/>
+    <row r="852" ht="14.25" customHeight="1"/>
+    <row r="853" ht="14.25" customHeight="1"/>
+    <row r="854" ht="14.25" customHeight="1"/>
+    <row r="855" ht="14.25" customHeight="1"/>
+    <row r="856" ht="14.25" customHeight="1"/>
+    <row r="857" ht="14.25" customHeight="1"/>
+    <row r="858" ht="14.25" customHeight="1"/>
+    <row r="859" ht="14.25" customHeight="1"/>
+    <row r="860" ht="14.25" customHeight="1"/>
+    <row r="861" ht="14.25" customHeight="1"/>
+    <row r="862" ht="14.25" customHeight="1"/>
+    <row r="863" ht="14.25" customHeight="1"/>
+    <row r="864" ht="14.25" customHeight="1"/>
+    <row r="865" ht="14.25" customHeight="1"/>
+    <row r="866" ht="14.25" customHeight="1"/>
+    <row r="867" ht="14.25" customHeight="1"/>
+    <row r="868" ht="14.25" customHeight="1"/>
+    <row r="869" ht="14.25" customHeight="1"/>
+    <row r="870" ht="14.25" customHeight="1"/>
+    <row r="871" ht="14.25" customHeight="1"/>
+    <row r="872" ht="14.25" customHeight="1"/>
+    <row r="873" ht="14.25" customHeight="1"/>
+    <row r="874" ht="14.25" customHeight="1"/>
+    <row r="875" ht="14.25" customHeight="1"/>
+    <row r="876" ht="14.25" customHeight="1"/>
+    <row r="877" ht="14.25" customHeight="1"/>
+    <row r="878" ht="14.25" customHeight="1"/>
+    <row r="879" ht="14.25" customHeight="1"/>
+    <row r="880" ht="14.25" customHeight="1"/>
+    <row r="881" ht="14.25" customHeight="1"/>
+    <row r="882" ht="14.25" customHeight="1"/>
+    <row r="883" ht="14.25" customHeight="1"/>
+    <row r="884" ht="14.25" customHeight="1"/>
+    <row r="885" ht="14.25" customHeight="1"/>
+    <row r="886" ht="14.25" customHeight="1"/>
+    <row r="887" ht="14.25" customHeight="1"/>
+    <row r="888" ht="14.25" customHeight="1"/>
+    <row r="889" ht="14.25" customHeight="1"/>
+    <row r="890" ht="14.25" customHeight="1"/>
+    <row r="891" ht="14.25" customHeight="1"/>
+    <row r="892" ht="14.25" customHeight="1"/>
+    <row r="893" ht="14.25" customHeight="1"/>
+    <row r="894" ht="14.25" customHeight="1"/>
+    <row r="895" ht="14.25" customHeight="1"/>
+    <row r="896" ht="14.25" customHeight="1"/>
+    <row r="897" ht="14.25" customHeight="1"/>
+    <row r="898" ht="14.25" customHeight="1"/>
+    <row r="899" ht="14.25" customHeight="1"/>
+    <row r="900" ht="14.25" customHeight="1"/>
+    <row r="901" ht="14.25" customHeight="1"/>
+    <row r="902" ht="14.25" customHeight="1"/>
+    <row r="903" ht="14.25" customHeight="1"/>
+    <row r="904" ht="14.25" customHeight="1"/>
+    <row r="905" ht="14.25" customHeight="1"/>
+    <row r="906" ht="14.25" customHeight="1"/>
+    <row r="907" ht="14.25" customHeight="1"/>
+    <row r="908" ht="14.25" customHeight="1"/>
+    <row r="909" ht="14.25" customHeight="1"/>
+    <row r="910" ht="14.25" customHeight="1"/>
+    <row r="911" ht="14.25" customHeight="1"/>
+    <row r="912" ht="14.25" customHeight="1"/>
+    <row r="913" ht="14.25" customHeight="1"/>
+    <row r="914" ht="14.25" customHeight="1"/>
+    <row r="915" ht="14.25" customHeight="1"/>
+    <row r="916" ht="14.25" customHeight="1"/>
+    <row r="917" ht="14.25" customHeight="1"/>
+    <row r="918" ht="14.25" customHeight="1"/>
+    <row r="919" ht="14.25" customHeight="1"/>
+    <row r="920" ht="14.25" customHeight="1"/>
+    <row r="921" ht="14.25" customHeight="1"/>
+    <row r="922" ht="14.25" customHeight="1"/>
+    <row r="923" ht="14.25" customHeight="1"/>
+    <row r="924" ht="14.25" customHeight="1"/>
+    <row r="925" ht="14.25" customHeight="1"/>
+    <row r="926" ht="14.25" customHeight="1"/>
+    <row r="927" ht="14.25" customHeight="1"/>
+    <row r="928" ht="14.25" customHeight="1"/>
+    <row r="929" ht="14.25" customHeight="1"/>
+    <row r="930" ht="14.25" customHeight="1"/>
+    <row r="931" ht="14.25" customHeight="1"/>
+    <row r="932" ht="14.25" customHeight="1"/>
+    <row r="933" ht="14.25" customHeight="1"/>
+    <row r="934" ht="14.25" customHeight="1"/>
+    <row r="935" ht="14.25" customHeight="1"/>
+    <row r="936" ht="14.25" customHeight="1"/>
+    <row r="937" ht="14.25" customHeight="1"/>
+    <row r="938" ht="14.25" customHeight="1"/>
+    <row r="939" ht="14.25" customHeight="1"/>
+    <row r="940" ht="14.25" customHeight="1"/>
+    <row r="941" ht="14.25" customHeight="1"/>
+    <row r="942" ht="14.25" customHeight="1"/>
+    <row r="943" ht="14.25" customHeight="1"/>
+    <row r="944" ht="14.25" customHeight="1"/>
+    <row r="945" ht="14.25" customHeight="1"/>
+    <row r="946" ht="14.25" customHeight="1"/>
+    <row r="947" ht="14.25" customHeight="1"/>
+    <row r="948" ht="14.25" customHeight="1"/>
+    <row r="949" ht="14.25" customHeight="1"/>
+    <row r="950" ht="14.25" customHeight="1"/>
+    <row r="951" ht="14.25" customHeight="1"/>
+    <row r="952" ht="14.25" customHeight="1"/>
+    <row r="953" ht="14.25" customHeight="1"/>
+    <row r="954" ht="14.25" customHeight="1"/>
+    <row r="955" ht="14.25" customHeight="1"/>
+    <row r="956" ht="14.25" customHeight="1"/>
+    <row r="957" ht="14.25" customHeight="1"/>
+    <row r="958" ht="14.25" customHeight="1"/>
+    <row r="959" ht="14.25" customHeight="1"/>
+    <row r="960" ht="14.25" customHeight="1"/>
+    <row r="961" ht="14.25" customHeight="1"/>
+    <row r="962" ht="14.25" customHeight="1"/>
+    <row r="963" ht="14.25" customHeight="1"/>
+    <row r="964" ht="14.25" customHeight="1"/>
+    <row r="965" ht="14.25" customHeight="1"/>
+    <row r="966" ht="14.25" customHeight="1"/>
+    <row r="967" ht="14.25" customHeight="1"/>
+    <row r="968" ht="14.25" customHeight="1"/>
+    <row r="969" ht="14.25" customHeight="1"/>
+    <row r="970" ht="14.25" customHeight="1"/>
+    <row r="971" ht="14.25" customHeight="1"/>
+    <row r="972" ht="14.25" customHeight="1"/>
+    <row r="973" ht="14.25" customHeight="1"/>
+    <row r="974" ht="14.25" customHeight="1"/>
+    <row r="975" ht="14.25" customHeight="1"/>
+    <row r="976" ht="14.25" customHeight="1"/>
+    <row r="977" ht="14.25" customHeight="1"/>
+    <row r="978" ht="14.25" customHeight="1"/>
+    <row r="979" ht="14.25" customHeight="1"/>
+    <row r="980" ht="14.25" customHeight="1"/>
+    <row r="981" ht="14.25" customHeight="1"/>
+    <row r="982" ht="14.25" customHeight="1"/>
+    <row r="983" ht="14.25" customHeight="1"/>
+    <row r="984" ht="14.25" customHeight="1"/>
+    <row r="985" ht="14.25" customHeight="1"/>
+    <row r="986" ht="14.25" customHeight="1"/>
+    <row r="987" ht="14.25" customHeight="1"/>
+    <row r="988" ht="14.25" customHeight="1"/>
+    <row r="989" ht="14.25" customHeight="1"/>
+    <row r="990" ht="14.25" customHeight="1"/>
+    <row r="991" ht="14.25" customHeight="1"/>
+    <row r="992" ht="14.25" customHeight="1"/>
+    <row r="993" ht="14.25" customHeight="1"/>
+    <row r="994" ht="14.25" customHeight="1"/>
+    <row r="995" ht="14.25" customHeight="1"/>
+    <row r="996" ht="14.25" customHeight="1"/>
+    <row r="997" ht="14.25" customHeight="1"/>
+    <row r="998" ht="14.25" customHeight="1"/>
+    <row r="999" ht="14.25" customHeight="1"/>
+    <row r="1000" ht="14.25" customHeight="1"/>
+    <row r="1001" ht="14.25" customHeight="1"/>
+    <row r="1002" ht="14.25" customHeight="1"/>
+    <row r="1003" ht="14.25" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <hyperlinks>
+    <hyperlink ref="C25" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="C33" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="C45" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1D4ED8"/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L1000"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="12" width="12" customWidth="1"/>
+    <col min="13" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-    </row>
-    <row r="2" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-    </row>
-    <row r="4" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="J4" s="7"/>
-      <c r="K4" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="L4" s="6"/>
-    </row>
-    <row r="5" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+    <row r="1" spans="1:12" ht="36" customHeight="1">
+      <c r="A1" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="42"/>
+    </row>
+    <row r="2" spans="1:12" ht="21.75" customHeight="1">
+      <c r="A2" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="42"/>
+    </row>
+    <row r="3" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="4" spans="1:12" ht="24" customHeight="1">
+      <c r="A4" s="48" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="46"/>
+      <c r="C4" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="F4" s="46"/>
+      <c r="G4" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="H4" s="46"/>
+      <c r="I4" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="J4" s="46"/>
+      <c r="K4" s="50" t="s">
+        <v>188</v>
+      </c>
+      <c r="L4" s="46"/>
+    </row>
+    <row r="5" spans="1:12" ht="43.5" customHeight="1">
+      <c r="A5" s="54">
         <f>COUNTA(#REF!)</f>
         <v>1</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5" t="e">
+      <c r="B5" s="46"/>
+      <c r="C5" s="54" t="e">
         <f>COUNTIF(#REF!,"Unread")</f>
         <v>#REF!</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5" t="e">
+      <c r="D5" s="46"/>
+      <c r="E5" s="54" t="e">
         <f>COUNTIF(#REF!,"Read")</f>
         <v>#REF!</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5" t="e">
+      <c r="F5" s="46"/>
+      <c r="G5" s="54" t="e">
         <f>COUNTIF(#REF!,"Work")</f>
         <v>#REF!</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5" t="e">
+      <c r="H5" s="46"/>
+      <c r="I5" s="54" t="e">
         <f>COUNTIF(#REF!,"Finance")</f>
         <v>#REF!</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5" t="e">
+      <c r="J5" s="46"/>
+      <c r="K5" s="54" t="e">
         <f>COUNTIF(#REF!,"Orders")</f>
         <v>#REF!</v>
       </c>
-      <c r="L5" s="5"/>
-    </row>
-    <row r="7" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="E7" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="I7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="F8" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="I8" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="J8" s="27" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="28" t="s">
+      <c r="L5" s="46"/>
+    </row>
+    <row r="6" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="7" spans="1:12" ht="27.75" customHeight="1">
+      <c r="A7" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" s="41"/>
+      <c r="C7" s="42"/>
+      <c r="E7" s="52" t="s">
+        <v>190</v>
+      </c>
+      <c r="F7" s="41"/>
+      <c r="G7" s="42"/>
+      <c r="I7" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="42"/>
+    </row>
+    <row r="8" spans="1:12" ht="24" customHeight="1">
+      <c r="A8" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="J8" s="22" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="21.75" customHeight="1">
+      <c r="A9" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="15" t="e">
+      <c r="B9" s="2" t="e">
         <f>COUNTIF(#REF!,A9)</f>
         <v>#REF!</v>
       </c>
-      <c r="C9" s="19" t="e">
+      <c r="C9" s="6" t="e">
         <f>IF(B9=0,"0%",TEXT(B9/SUM(B9:B14),"0.0%"))</f>
         <v>#REF!</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="15" t="e">
+      <c r="F9" s="2" t="e">
         <f>COUNTIF(#REF!,E9)</f>
         <v>#REF!</v>
       </c>
-      <c r="G9" s="19" t="e">
+      <c r="G9" s="6" t="e">
         <f>IF(F9=0,"0%",TEXT(F9/SUM(F9:F10),"0.0%"))</f>
         <v>#REF!</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="19">
+      <c r="J9" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="30" t="s">
+    <row r="10" spans="1:12" ht="21.75" customHeight="1">
+      <c r="A10" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="15" t="e">
+      <c r="B10" s="2" t="e">
         <f>COUNTIF(#REF!,A10)</f>
         <v>#REF!</v>
       </c>
-      <c r="C10" s="19" t="e">
+      <c r="C10" s="6" t="e">
         <f>IF(B10=0,"0%",TEXT(B10/SUM(B9:B14),"0.0%"))</f>
         <v>#REF!</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="15" t="e">
+      <c r="F10" s="2" t="e">
         <f>COUNTIF(#REF!,E10)</f>
         <v>#REF!</v>
       </c>
-      <c r="G10" s="19" t="e">
+      <c r="G10" s="6" t="e">
         <f>IF(F10=0,"0%",TEXT(F10/SUM(F9:F10),"0.0%"))</f>
         <v>#REF!</v>
       </c>
-      <c r="I10" s="31" t="s">
+      <c r="I10" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="32" t="s">
+    <row r="11" spans="1:12" ht="21.75" customHeight="1">
+      <c r="A11" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="15" t="e">
+      <c r="B11" s="2" t="e">
         <f>COUNTIF(#REF!,A11)</f>
         <v>#REF!</v>
       </c>
-      <c r="C11" s="19" t="e">
+      <c r="C11" s="6" t="e">
         <f>IF(B11=0,"0%",TEXT(B11/SUM(B9:B14),"0.0%"))</f>
         <v>#REF!</v>
       </c>
-      <c r="I11" s="29" t="s">
+      <c r="I11" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="33" t="s">
+    <row r="12" spans="1:12" ht="21.75" customHeight="1">
+      <c r="A12" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="15" t="e">
+      <c r="B12" s="2" t="e">
         <f>COUNTIF(#REF!,A12)</f>
         <v>#REF!</v>
       </c>
-      <c r="C12" s="19" t="e">
+      <c r="C12" s="6" t="e">
         <f>IF(B12=0,"0%",TEXT(B12/SUM(B9:B14),"0.0%"))</f>
         <v>#REF!</v>
       </c>
-      <c r="I12" s="31" t="s">
+      <c r="I12" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="34" t="s">
+    <row r="13" spans="1:12" ht="21.75" customHeight="1">
+      <c r="A13" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="15" t="e">
+      <c r="B13" s="2" t="e">
         <f>COUNTIF(#REF!,A13)</f>
         <v>#REF!</v>
       </c>
-      <c r="C13" s="19" t="e">
+      <c r="C13" s="6" t="e">
         <f>IF(B13=0,"0%",TEXT(B13/SUM(B9:B14),"0.0%"))</f>
         <v>#REF!</v>
       </c>
-      <c r="I13" s="29" t="s">
+      <c r="I13" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="29" t="s">
+    <row r="14" spans="1:12" ht="21.75" customHeight="1">
+      <c r="A14" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="15" t="e">
+      <c r="B14" s="2" t="e">
         <f>COUNTIF(#REF!,A14)</f>
         <v>#REF!</v>
       </c>
-      <c r="C14" s="19" t="e">
+      <c r="C14" s="6" t="e">
         <f>IF(B14=0,"0%",TEXT(B14/SUM(B9:B14),"0.0%"))</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-    </row>
+    <row r="15" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="16" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="17" spans="1:12" ht="27.75" customHeight="1">
+      <c r="A17" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="42"/>
+    </row>
+    <row r="18" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="19" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="20" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="21" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="22" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="23" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="24" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="25" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="26" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="27" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="28" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="31" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:12" ht="14.25" customHeight="1"/>
+    <row r="33" ht="14.25" customHeight="1"/>
+    <row r="34" ht="14.25" customHeight="1"/>
+    <row r="35" ht="14.25" customHeight="1"/>
+    <row r="36" ht="14.25" customHeight="1"/>
+    <row r="37" ht="14.25" customHeight="1"/>
+    <row r="38" ht="14.25" customHeight="1"/>
+    <row r="39" ht="14.25" customHeight="1"/>
+    <row r="40" ht="14.25" customHeight="1"/>
+    <row r="41" ht="14.25" customHeight="1"/>
+    <row r="42" ht="14.25" customHeight="1"/>
+    <row r="43" ht="14.25" customHeight="1"/>
+    <row r="44" ht="14.25" customHeight="1"/>
+    <row r="45" ht="14.25" customHeight="1"/>
+    <row r="46" ht="14.25" customHeight="1"/>
+    <row r="47" ht="14.25" customHeight="1"/>
+    <row r="48" ht="14.25" customHeight="1"/>
+    <row r="49" ht="14.25" customHeight="1"/>
+    <row r="50" ht="14.25" customHeight="1"/>
+    <row r="51" ht="14.25" customHeight="1"/>
+    <row r="52" ht="14.25" customHeight="1"/>
+    <row r="53" ht="14.25" customHeight="1"/>
+    <row r="54" ht="14.25" customHeight="1"/>
+    <row r="55" ht="14.25" customHeight="1"/>
+    <row r="56" ht="14.25" customHeight="1"/>
+    <row r="57" ht="14.25" customHeight="1"/>
+    <row r="58" ht="14.25" customHeight="1"/>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
+    <row r="74" ht="14.25" customHeight="1"/>
+    <row r="75" ht="14.25" customHeight="1"/>
+    <row r="76" ht="14.25" customHeight="1"/>
+    <row r="77" ht="14.25" customHeight="1"/>
+    <row r="78" ht="14.25" customHeight="1"/>
+    <row r="79" ht="14.25" customHeight="1"/>
+    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="81" ht="14.25" customHeight="1"/>
+    <row r="82" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1"/>
+    <row r="85" ht="14.25" customHeight="1"/>
+    <row r="86" ht="14.25" customHeight="1"/>
+    <row r="87" ht="14.25" customHeight="1"/>
+    <row r="88" ht="14.25" customHeight="1"/>
+    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
+    <row r="95" ht="14.25" customHeight="1"/>
+    <row r="96" ht="14.25" customHeight="1"/>
+    <row r="97" ht="14.25" customHeight="1"/>
+    <row r="98" ht="14.25" customHeight="1"/>
+    <row r="99" ht="14.25" customHeight="1"/>
+    <row r="100" ht="14.25" customHeight="1"/>
+    <row r="101" ht="14.25" customHeight="1"/>
+    <row r="102" ht="14.25" customHeight="1"/>
+    <row r="103" ht="14.25" customHeight="1"/>
+    <row r="104" ht="14.25" customHeight="1"/>
+    <row r="105" ht="14.25" customHeight="1"/>
+    <row r="106" ht="14.25" customHeight="1"/>
+    <row r="107" ht="14.25" customHeight="1"/>
+    <row r="108" ht="14.25" customHeight="1"/>
+    <row r="109" ht="14.25" customHeight="1"/>
+    <row r="110" ht="14.25" customHeight="1"/>
+    <row r="111" ht="14.25" customHeight="1"/>
+    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="113" ht="14.25" customHeight="1"/>
+    <row r="114" ht="14.25" customHeight="1"/>
+    <row r="115" ht="14.25" customHeight="1"/>
+    <row r="116" ht="14.25" customHeight="1"/>
+    <row r="117" ht="14.25" customHeight="1"/>
+    <row r="118" ht="14.25" customHeight="1"/>
+    <row r="119" ht="14.25" customHeight="1"/>
+    <row r="120" ht="14.25" customHeight="1"/>
+    <row r="121" ht="14.25" customHeight="1"/>
+    <row r="122" ht="14.25" customHeight="1"/>
+    <row r="123" ht="14.25" customHeight="1"/>
+    <row r="124" ht="14.25" customHeight="1"/>
+    <row r="125" ht="14.25" customHeight="1"/>
+    <row r="126" ht="14.25" customHeight="1"/>
+    <row r="127" ht="14.25" customHeight="1"/>
+    <row r="128" ht="14.25" customHeight="1"/>
+    <row r="129" ht="14.25" customHeight="1"/>
+    <row r="130" ht="14.25" customHeight="1"/>
+    <row r="131" ht="14.25" customHeight="1"/>
+    <row r="132" ht="14.25" customHeight="1"/>
+    <row r="133" ht="14.25" customHeight="1"/>
+    <row r="134" ht="14.25" customHeight="1"/>
+    <row r="135" ht="14.25" customHeight="1"/>
+    <row r="136" ht="14.25" customHeight="1"/>
+    <row r="137" ht="14.25" customHeight="1"/>
+    <row r="138" ht="14.25" customHeight="1"/>
+    <row r="139" ht="14.25" customHeight="1"/>
+    <row r="140" ht="14.25" customHeight="1"/>
+    <row r="141" ht="14.25" customHeight="1"/>
+    <row r="142" ht="14.25" customHeight="1"/>
+    <row r="143" ht="14.25" customHeight="1"/>
+    <row r="144" ht="14.25" customHeight="1"/>
+    <row r="145" ht="14.25" customHeight="1"/>
+    <row r="146" ht="14.25" customHeight="1"/>
+    <row r="147" ht="14.25" customHeight="1"/>
+    <row r="148" ht="14.25" customHeight="1"/>
+    <row r="149" ht="14.25" customHeight="1"/>
+    <row r="150" ht="14.25" customHeight="1"/>
+    <row r="151" ht="14.25" customHeight="1"/>
+    <row r="152" ht="14.25" customHeight="1"/>
+    <row r="153" ht="14.25" customHeight="1"/>
+    <row r="154" ht="14.25" customHeight="1"/>
+    <row r="155" ht="14.25" customHeight="1"/>
+    <row r="156" ht="14.25" customHeight="1"/>
+    <row r="157" ht="14.25" customHeight="1"/>
+    <row r="158" ht="14.25" customHeight="1"/>
+    <row r="159" ht="14.25" customHeight="1"/>
+    <row r="160" ht="14.25" customHeight="1"/>
+    <row r="161" ht="14.25" customHeight="1"/>
+    <row r="162" ht="14.25" customHeight="1"/>
+    <row r="163" ht="14.25" customHeight="1"/>
+    <row r="164" ht="14.25" customHeight="1"/>
+    <row r="165" ht="14.25" customHeight="1"/>
+    <row r="166" ht="14.25" customHeight="1"/>
+    <row r="167" ht="14.25" customHeight="1"/>
+    <row r="168" ht="14.25" customHeight="1"/>
+    <row r="169" ht="14.25" customHeight="1"/>
+    <row r="170" ht="14.25" customHeight="1"/>
+    <row r="171" ht="14.25" customHeight="1"/>
+    <row r="172" ht="14.25" customHeight="1"/>
+    <row r="173" ht="14.25" customHeight="1"/>
+    <row r="174" ht="14.25" customHeight="1"/>
+    <row r="175" ht="14.25" customHeight="1"/>
+    <row r="176" ht="14.25" customHeight="1"/>
+    <row r="177" ht="14.25" customHeight="1"/>
+    <row r="178" ht="14.25" customHeight="1"/>
+    <row r="179" ht="14.25" customHeight="1"/>
+    <row r="180" ht="14.25" customHeight="1"/>
+    <row r="181" ht="14.25" customHeight="1"/>
+    <row r="182" ht="14.25" customHeight="1"/>
+    <row r="183" ht="14.25" customHeight="1"/>
+    <row r="184" ht="14.25" customHeight="1"/>
+    <row r="185" ht="14.25" customHeight="1"/>
+    <row r="186" ht="14.25" customHeight="1"/>
+    <row r="187" ht="14.25" customHeight="1"/>
+    <row r="188" ht="14.25" customHeight="1"/>
+    <row r="189" ht="14.25" customHeight="1"/>
+    <row r="190" ht="14.25" customHeight="1"/>
+    <row r="191" ht="14.25" customHeight="1"/>
+    <row r="192" ht="14.25" customHeight="1"/>
+    <row r="193" ht="14.25" customHeight="1"/>
+    <row r="194" ht="14.25" customHeight="1"/>
+    <row r="195" ht="14.25" customHeight="1"/>
+    <row r="196" ht="14.25" customHeight="1"/>
+    <row r="197" ht="14.25" customHeight="1"/>
+    <row r="198" ht="14.25" customHeight="1"/>
+    <row r="199" ht="14.25" customHeight="1"/>
+    <row r="200" ht="14.25" customHeight="1"/>
+    <row r="201" ht="14.25" customHeight="1"/>
+    <row r="202" ht="14.25" customHeight="1"/>
+    <row r="203" ht="14.25" customHeight="1"/>
+    <row r="204" ht="14.25" customHeight="1"/>
+    <row r="205" ht="14.25" customHeight="1"/>
+    <row r="206" ht="14.25" customHeight="1"/>
+    <row r="207" ht="14.25" customHeight="1"/>
+    <row r="208" ht="14.25" customHeight="1"/>
+    <row r="209" ht="14.25" customHeight="1"/>
+    <row r="210" ht="14.25" customHeight="1"/>
+    <row r="211" ht="14.25" customHeight="1"/>
+    <row r="212" ht="14.25" customHeight="1"/>
+    <row r="213" ht="14.25" customHeight="1"/>
+    <row r="214" ht="14.25" customHeight="1"/>
+    <row r="215" ht="14.25" customHeight="1"/>
+    <row r="216" ht="14.25" customHeight="1"/>
+    <row r="217" ht="14.25" customHeight="1"/>
+    <row r="218" ht="14.25" customHeight="1"/>
+    <row r="219" ht="14.25" customHeight="1"/>
+    <row r="220" ht="14.25" customHeight="1"/>
+    <row r="221" ht="14.25" customHeight="1"/>
+    <row r="222" ht="14.25" customHeight="1"/>
+    <row r="223" ht="14.25" customHeight="1"/>
+    <row r="224" ht="14.25" customHeight="1"/>
+    <row r="225" ht="14.25" customHeight="1"/>
+    <row r="226" ht="14.25" customHeight="1"/>
+    <row r="227" ht="14.25" customHeight="1"/>
+    <row r="228" ht="14.25" customHeight="1"/>
+    <row r="229" ht="14.25" customHeight="1"/>
+    <row r="230" ht="14.25" customHeight="1"/>
+    <row r="231" ht="14.25" customHeight="1"/>
+    <row r="232" ht="14.25" customHeight="1"/>
+    <row r="233" ht="14.25" customHeight="1"/>
+    <row r="234" ht="14.25" customHeight="1"/>
+    <row r="235" ht="14.25" customHeight="1"/>
+    <row r="236" ht="14.25" customHeight="1"/>
+    <row r="237" ht="14.25" customHeight="1"/>
+    <row r="238" ht="14.25" customHeight="1"/>
+    <row r="239" ht="14.25" customHeight="1"/>
+    <row r="240" ht="14.25" customHeight="1"/>
+    <row r="241" ht="14.25" customHeight="1"/>
+    <row r="242" ht="14.25" customHeight="1"/>
+    <row r="243" ht="14.25" customHeight="1"/>
+    <row r="244" ht="14.25" customHeight="1"/>
+    <row r="245" ht="14.25" customHeight="1"/>
+    <row r="246" ht="14.25" customHeight="1"/>
+    <row r="247" ht="14.25" customHeight="1"/>
+    <row r="248" ht="14.25" customHeight="1"/>
+    <row r="249" ht="14.25" customHeight="1"/>
+    <row r="250" ht="14.25" customHeight="1"/>
+    <row r="251" ht="14.25" customHeight="1"/>
+    <row r="252" ht="14.25" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
+    <row r="254" ht="14.25" customHeight="1"/>
+    <row r="255" ht="14.25" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
+    <row r="257" ht="14.25" customHeight="1"/>
+    <row r="258" ht="14.25" customHeight="1"/>
+    <row r="259" ht="14.25" customHeight="1"/>
+    <row r="260" ht="14.25" customHeight="1"/>
+    <row r="261" ht="14.25" customHeight="1"/>
+    <row r="262" ht="14.25" customHeight="1"/>
+    <row r="263" ht="14.25" customHeight="1"/>
+    <row r="264" ht="14.25" customHeight="1"/>
+    <row r="265" ht="14.25" customHeight="1"/>
+    <row r="266" ht="14.25" customHeight="1"/>
+    <row r="267" ht="14.25" customHeight="1"/>
+    <row r="268" ht="14.25" customHeight="1"/>
+    <row r="269" ht="14.25" customHeight="1"/>
+    <row r="270" ht="14.25" customHeight="1"/>
+    <row r="271" ht="14.25" customHeight="1"/>
+    <row r="272" ht="14.25" customHeight="1"/>
+    <row r="273" ht="14.25" customHeight="1"/>
+    <row r="274" ht="14.25" customHeight="1"/>
+    <row r="275" ht="14.25" customHeight="1"/>
+    <row r="276" ht="14.25" customHeight="1"/>
+    <row r="277" ht="14.25" customHeight="1"/>
+    <row r="278" ht="14.25" customHeight="1"/>
+    <row r="279" ht="14.25" customHeight="1"/>
+    <row r="280" ht="14.25" customHeight="1"/>
+    <row r="281" ht="14.25" customHeight="1"/>
+    <row r="282" ht="14.25" customHeight="1"/>
+    <row r="283" ht="14.25" customHeight="1"/>
+    <row r="284" ht="14.25" customHeight="1"/>
+    <row r="285" ht="14.25" customHeight="1"/>
+    <row r="286" ht="14.25" customHeight="1"/>
+    <row r="287" ht="14.25" customHeight="1"/>
+    <row r="288" ht="14.25" customHeight="1"/>
+    <row r="289" ht="14.25" customHeight="1"/>
+    <row r="290" ht="14.25" customHeight="1"/>
+    <row r="291" ht="14.25" customHeight="1"/>
+    <row r="292" ht="14.25" customHeight="1"/>
+    <row r="293" ht="14.25" customHeight="1"/>
+    <row r="294" ht="14.25" customHeight="1"/>
+    <row r="295" ht="14.25" customHeight="1"/>
+    <row r="296" ht="14.25" customHeight="1"/>
+    <row r="297" ht="14.25" customHeight="1"/>
+    <row r="298" ht="14.25" customHeight="1"/>
+    <row r="299" ht="14.25" customHeight="1"/>
+    <row r="300" ht="14.25" customHeight="1"/>
+    <row r="301" ht="14.25" customHeight="1"/>
+    <row r="302" ht="14.25" customHeight="1"/>
+    <row r="303" ht="14.25" customHeight="1"/>
+    <row r="304" ht="14.25" customHeight="1"/>
+    <row r="305" ht="14.25" customHeight="1"/>
+    <row r="306" ht="14.25" customHeight="1"/>
+    <row r="307" ht="14.25" customHeight="1"/>
+    <row r="308" ht="14.25" customHeight="1"/>
+    <row r="309" ht="14.25" customHeight="1"/>
+    <row r="310" ht="14.25" customHeight="1"/>
+    <row r="311" ht="14.25" customHeight="1"/>
+    <row r="312" ht="14.25" customHeight="1"/>
+    <row r="313" ht="14.25" customHeight="1"/>
+    <row r="314" ht="14.25" customHeight="1"/>
+    <row r="315" ht="14.25" customHeight="1"/>
+    <row r="316" ht="14.25" customHeight="1"/>
+    <row r="317" ht="14.25" customHeight="1"/>
+    <row r="318" ht="14.25" customHeight="1"/>
+    <row r="319" ht="14.25" customHeight="1"/>
+    <row r="320" ht="14.25" customHeight="1"/>
+    <row r="321" ht="14.25" customHeight="1"/>
+    <row r="322" ht="14.25" customHeight="1"/>
+    <row r="323" ht="14.25" customHeight="1"/>
+    <row r="324" ht="14.25" customHeight="1"/>
+    <row r="325" ht="14.25" customHeight="1"/>
+    <row r="326" ht="14.25" customHeight="1"/>
+    <row r="327" ht="14.25" customHeight="1"/>
+    <row r="328" ht="14.25" customHeight="1"/>
+    <row r="329" ht="14.25" customHeight="1"/>
+    <row r="330" ht="14.25" customHeight="1"/>
+    <row r="331" ht="14.25" customHeight="1"/>
+    <row r="332" ht="14.25" customHeight="1"/>
+    <row r="333" ht="14.25" customHeight="1"/>
+    <row r="334" ht="14.25" customHeight="1"/>
+    <row r="335" ht="14.25" customHeight="1"/>
+    <row r="336" ht="14.25" customHeight="1"/>
+    <row r="337" ht="14.25" customHeight="1"/>
+    <row r="338" ht="14.25" customHeight="1"/>
+    <row r="339" ht="14.25" customHeight="1"/>
+    <row r="340" ht="14.25" customHeight="1"/>
+    <row r="341" ht="14.25" customHeight="1"/>
+    <row r="342" ht="14.25" customHeight="1"/>
+    <row r="343" ht="14.25" customHeight="1"/>
+    <row r="344" ht="14.25" customHeight="1"/>
+    <row r="345" ht="14.25" customHeight="1"/>
+    <row r="346" ht="14.25" customHeight="1"/>
+    <row r="347" ht="14.25" customHeight="1"/>
+    <row r="348" ht="14.25" customHeight="1"/>
+    <row r="349" ht="14.25" customHeight="1"/>
+    <row r="350" ht="14.25" customHeight="1"/>
+    <row r="351" ht="14.25" customHeight="1"/>
+    <row r="352" ht="14.25" customHeight="1"/>
+    <row r="353" ht="14.25" customHeight="1"/>
+    <row r="354" ht="14.25" customHeight="1"/>
+    <row r="355" ht="14.25" customHeight="1"/>
+    <row r="356" ht="14.25" customHeight="1"/>
+    <row r="357" ht="14.25" customHeight="1"/>
+    <row r="358" ht="14.25" customHeight="1"/>
+    <row r="359" ht="14.25" customHeight="1"/>
+    <row r="360" ht="14.25" customHeight="1"/>
+    <row r="361" ht="14.25" customHeight="1"/>
+    <row r="362" ht="14.25" customHeight="1"/>
+    <row r="363" ht="14.25" customHeight="1"/>
+    <row r="364" ht="14.25" customHeight="1"/>
+    <row r="365" ht="14.25" customHeight="1"/>
+    <row r="366" ht="14.25" customHeight="1"/>
+    <row r="367" ht="14.25" customHeight="1"/>
+    <row r="368" ht="14.25" customHeight="1"/>
+    <row r="369" ht="14.25" customHeight="1"/>
+    <row r="370" ht="14.25" customHeight="1"/>
+    <row r="371" ht="14.25" customHeight="1"/>
+    <row r="372" ht="14.25" customHeight="1"/>
+    <row r="373" ht="14.25" customHeight="1"/>
+    <row r="374" ht="14.25" customHeight="1"/>
+    <row r="375" ht="14.25" customHeight="1"/>
+    <row r="376" ht="14.25" customHeight="1"/>
+    <row r="377" ht="14.25" customHeight="1"/>
+    <row r="378" ht="14.25" customHeight="1"/>
+    <row r="379" ht="14.25" customHeight="1"/>
+    <row r="380" ht="14.25" customHeight="1"/>
+    <row r="381" ht="14.25" customHeight="1"/>
+    <row r="382" ht="14.25" customHeight="1"/>
+    <row r="383" ht="14.25" customHeight="1"/>
+    <row r="384" ht="14.25" customHeight="1"/>
+    <row r="385" ht="14.25" customHeight="1"/>
+    <row r="386" ht="14.25" customHeight="1"/>
+    <row r="387" ht="14.25" customHeight="1"/>
+    <row r="388" ht="14.25" customHeight="1"/>
+    <row r="389" ht="14.25" customHeight="1"/>
+    <row r="390" ht="14.25" customHeight="1"/>
+    <row r="391" ht="14.25" customHeight="1"/>
+    <row r="392" ht="14.25" customHeight="1"/>
+    <row r="393" ht="14.25" customHeight="1"/>
+    <row r="394" ht="14.25" customHeight="1"/>
+    <row r="395" ht="14.25" customHeight="1"/>
+    <row r="396" ht="14.25" customHeight="1"/>
+    <row r="397" ht="14.25" customHeight="1"/>
+    <row r="398" ht="14.25" customHeight="1"/>
+    <row r="399" ht="14.25" customHeight="1"/>
+    <row r="400" ht="14.25" customHeight="1"/>
+    <row r="401" ht="14.25" customHeight="1"/>
+    <row r="402" ht="14.25" customHeight="1"/>
+    <row r="403" ht="14.25" customHeight="1"/>
+    <row r="404" ht="14.25" customHeight="1"/>
+    <row r="405" ht="14.25" customHeight="1"/>
+    <row r="406" ht="14.25" customHeight="1"/>
+    <row r="407" ht="14.25" customHeight="1"/>
+    <row r="408" ht="14.25" customHeight="1"/>
+    <row r="409" ht="14.25" customHeight="1"/>
+    <row r="410" ht="14.25" customHeight="1"/>
+    <row r="411" ht="14.25" customHeight="1"/>
+    <row r="412" ht="14.25" customHeight="1"/>
+    <row r="413" ht="14.25" customHeight="1"/>
+    <row r="414" ht="14.25" customHeight="1"/>
+    <row r="415" ht="14.25" customHeight="1"/>
+    <row r="416" ht="14.25" customHeight="1"/>
+    <row r="417" ht="14.25" customHeight="1"/>
+    <row r="418" ht="14.25" customHeight="1"/>
+    <row r="419" ht="14.25" customHeight="1"/>
+    <row r="420" ht="14.25" customHeight="1"/>
+    <row r="421" ht="14.25" customHeight="1"/>
+    <row r="422" ht="14.25" customHeight="1"/>
+    <row r="423" ht="14.25" customHeight="1"/>
+    <row r="424" ht="14.25" customHeight="1"/>
+    <row r="425" ht="14.25" customHeight="1"/>
+    <row r="426" ht="14.25" customHeight="1"/>
+    <row r="427" ht="14.25" customHeight="1"/>
+    <row r="428" ht="14.25" customHeight="1"/>
+    <row r="429" ht="14.25" customHeight="1"/>
+    <row r="430" ht="14.25" customHeight="1"/>
+    <row r="431" ht="14.25" customHeight="1"/>
+    <row r="432" ht="14.25" customHeight="1"/>
+    <row r="433" ht="14.25" customHeight="1"/>
+    <row r="434" ht="14.25" customHeight="1"/>
+    <row r="435" ht="14.25" customHeight="1"/>
+    <row r="436" ht="14.25" customHeight="1"/>
+    <row r="437" ht="14.25" customHeight="1"/>
+    <row r="438" ht="14.25" customHeight="1"/>
+    <row r="439" ht="14.25" customHeight="1"/>
+    <row r="440" ht="14.25" customHeight="1"/>
+    <row r="441" ht="14.25" customHeight="1"/>
+    <row r="442" ht="14.25" customHeight="1"/>
+    <row r="443" ht="14.25" customHeight="1"/>
+    <row r="444" ht="14.25" customHeight="1"/>
+    <row r="445" ht="14.25" customHeight="1"/>
+    <row r="446" ht="14.25" customHeight="1"/>
+    <row r="447" ht="14.25" customHeight="1"/>
+    <row r="448" ht="14.25" customHeight="1"/>
+    <row r="449" ht="14.25" customHeight="1"/>
+    <row r="450" ht="14.25" customHeight="1"/>
+    <row r="451" ht="14.25" customHeight="1"/>
+    <row r="452" ht="14.25" customHeight="1"/>
+    <row r="453" ht="14.25" customHeight="1"/>
+    <row r="454" ht="14.25" customHeight="1"/>
+    <row r="455" ht="14.25" customHeight="1"/>
+    <row r="456" ht="14.25" customHeight="1"/>
+    <row r="457" ht="14.25" customHeight="1"/>
+    <row r="458" ht="14.25" customHeight="1"/>
+    <row r="459" ht="14.25" customHeight="1"/>
+    <row r="460" ht="14.25" customHeight="1"/>
+    <row r="461" ht="14.25" customHeight="1"/>
+    <row r="462" ht="14.25" customHeight="1"/>
+    <row r="463" ht="14.25" customHeight="1"/>
+    <row r="464" ht="14.25" customHeight="1"/>
+    <row r="465" ht="14.25" customHeight="1"/>
+    <row r="466" ht="14.25" customHeight="1"/>
+    <row r="467" ht="14.25" customHeight="1"/>
+    <row r="468" ht="14.25" customHeight="1"/>
+    <row r="469" ht="14.25" customHeight="1"/>
+    <row r="470" ht="14.25" customHeight="1"/>
+    <row r="471" ht="14.25" customHeight="1"/>
+    <row r="472" ht="14.25" customHeight="1"/>
+    <row r="473" ht="14.25" customHeight="1"/>
+    <row r="474" ht="14.25" customHeight="1"/>
+    <row r="475" ht="14.25" customHeight="1"/>
+    <row r="476" ht="14.25" customHeight="1"/>
+    <row r="477" ht="14.25" customHeight="1"/>
+    <row r="478" ht="14.25" customHeight="1"/>
+    <row r="479" ht="14.25" customHeight="1"/>
+    <row r="480" ht="14.25" customHeight="1"/>
+    <row r="481" ht="14.25" customHeight="1"/>
+    <row r="482" ht="14.25" customHeight="1"/>
+    <row r="483" ht="14.25" customHeight="1"/>
+    <row r="484" ht="14.25" customHeight="1"/>
+    <row r="485" ht="14.25" customHeight="1"/>
+    <row r="486" ht="14.25" customHeight="1"/>
+    <row r="487" ht="14.25" customHeight="1"/>
+    <row r="488" ht="14.25" customHeight="1"/>
+    <row r="489" ht="14.25" customHeight="1"/>
+    <row r="490" ht="14.25" customHeight="1"/>
+    <row r="491" ht="14.25" customHeight="1"/>
+    <row r="492" ht="14.25" customHeight="1"/>
+    <row r="493" ht="14.25" customHeight="1"/>
+    <row r="494" ht="14.25" customHeight="1"/>
+    <row r="495" ht="14.25" customHeight="1"/>
+    <row r="496" ht="14.25" customHeight="1"/>
+    <row r="497" ht="14.25" customHeight="1"/>
+    <row r="498" ht="14.25" customHeight="1"/>
+    <row r="499" ht="14.25" customHeight="1"/>
+    <row r="500" ht="14.25" customHeight="1"/>
+    <row r="501" ht="14.25" customHeight="1"/>
+    <row r="502" ht="14.25" customHeight="1"/>
+    <row r="503" ht="14.25" customHeight="1"/>
+    <row r="504" ht="14.25" customHeight="1"/>
+    <row r="505" ht="14.25" customHeight="1"/>
+    <row r="506" ht="14.25" customHeight="1"/>
+    <row r="507" ht="14.25" customHeight="1"/>
+    <row r="508" ht="14.25" customHeight="1"/>
+    <row r="509" ht="14.25" customHeight="1"/>
+    <row r="510" ht="14.25" customHeight="1"/>
+    <row r="511" ht="14.25" customHeight="1"/>
+    <row r="512" ht="14.25" customHeight="1"/>
+    <row r="513" ht="14.25" customHeight="1"/>
+    <row r="514" ht="14.25" customHeight="1"/>
+    <row r="515" ht="14.25" customHeight="1"/>
+    <row r="516" ht="14.25" customHeight="1"/>
+    <row r="517" ht="14.25" customHeight="1"/>
+    <row r="518" ht="14.25" customHeight="1"/>
+    <row r="519" ht="14.25" customHeight="1"/>
+    <row r="520" ht="14.25" customHeight="1"/>
+    <row r="521" ht="14.25" customHeight="1"/>
+    <row r="522" ht="14.25" customHeight="1"/>
+    <row r="523" ht="14.25" customHeight="1"/>
+    <row r="524" ht="14.25" customHeight="1"/>
+    <row r="525" ht="14.25" customHeight="1"/>
+    <row r="526" ht="14.25" customHeight="1"/>
+    <row r="527" ht="14.25" customHeight="1"/>
+    <row r="528" ht="14.25" customHeight="1"/>
+    <row r="529" ht="14.25" customHeight="1"/>
+    <row r="530" ht="14.25" customHeight="1"/>
+    <row r="531" ht="14.25" customHeight="1"/>
+    <row r="532" ht="14.25" customHeight="1"/>
+    <row r="533" ht="14.25" customHeight="1"/>
+    <row r="534" ht="14.25" customHeight="1"/>
+    <row r="535" ht="14.25" customHeight="1"/>
+    <row r="536" ht="14.25" customHeight="1"/>
+    <row r="537" ht="14.25" customHeight="1"/>
+    <row r="538" ht="14.25" customHeight="1"/>
+    <row r="539" ht="14.25" customHeight="1"/>
+    <row r="540" ht="14.25" customHeight="1"/>
+    <row r="541" ht="14.25" customHeight="1"/>
+    <row r="542" ht="14.25" customHeight="1"/>
+    <row r="543" ht="14.25" customHeight="1"/>
+    <row r="544" ht="14.25" customHeight="1"/>
+    <row r="545" ht="14.25" customHeight="1"/>
+    <row r="546" ht="14.25" customHeight="1"/>
+    <row r="547" ht="14.25" customHeight="1"/>
+    <row r="548" ht="14.25" customHeight="1"/>
+    <row r="549" ht="14.25" customHeight="1"/>
+    <row r="550" ht="14.25" customHeight="1"/>
+    <row r="551" ht="14.25" customHeight="1"/>
+    <row r="552" ht="14.25" customHeight="1"/>
+    <row r="553" ht="14.25" customHeight="1"/>
+    <row r="554" ht="14.25" customHeight="1"/>
+    <row r="555" ht="14.25" customHeight="1"/>
+    <row r="556" ht="14.25" customHeight="1"/>
+    <row r="557" ht="14.25" customHeight="1"/>
+    <row r="558" ht="14.25" customHeight="1"/>
+    <row r="559" ht="14.25" customHeight="1"/>
+    <row r="560" ht="14.25" customHeight="1"/>
+    <row r="561" ht="14.25" customHeight="1"/>
+    <row r="562" ht="14.25" customHeight="1"/>
+    <row r="563" ht="14.25" customHeight="1"/>
+    <row r="564" ht="14.25" customHeight="1"/>
+    <row r="565" ht="14.25" customHeight="1"/>
+    <row r="566" ht="14.25" customHeight="1"/>
+    <row r="567" ht="14.25" customHeight="1"/>
+    <row r="568" ht="14.25" customHeight="1"/>
+    <row r="569" ht="14.25" customHeight="1"/>
+    <row r="570" ht="14.25" customHeight="1"/>
+    <row r="571" ht="14.25" customHeight="1"/>
+    <row r="572" ht="14.25" customHeight="1"/>
+    <row r="573" ht="14.25" customHeight="1"/>
+    <row r="574" ht="14.25" customHeight="1"/>
+    <row r="575" ht="14.25" customHeight="1"/>
+    <row r="576" ht="14.25" customHeight="1"/>
+    <row r="577" ht="14.25" customHeight="1"/>
+    <row r="578" ht="14.25" customHeight="1"/>
+    <row r="579" ht="14.25" customHeight="1"/>
+    <row r="580" ht="14.25" customHeight="1"/>
+    <row r="581" ht="14.25" customHeight="1"/>
+    <row r="582" ht="14.25" customHeight="1"/>
+    <row r="583" ht="14.25" customHeight="1"/>
+    <row r="584" ht="14.25" customHeight="1"/>
+    <row r="585" ht="14.25" customHeight="1"/>
+    <row r="586" ht="14.25" customHeight="1"/>
+    <row r="587" ht="14.25" customHeight="1"/>
+    <row r="588" ht="14.25" customHeight="1"/>
+    <row r="589" ht="14.25" customHeight="1"/>
+    <row r="590" ht="14.25" customHeight="1"/>
+    <row r="591" ht="14.25" customHeight="1"/>
+    <row r="592" ht="14.25" customHeight="1"/>
+    <row r="593" ht="14.25" customHeight="1"/>
+    <row r="594" ht="14.25" customHeight="1"/>
+    <row r="595" ht="14.25" customHeight="1"/>
+    <row r="596" ht="14.25" customHeight="1"/>
+    <row r="597" ht="14.25" customHeight="1"/>
+    <row r="598" ht="14.25" customHeight="1"/>
+    <row r="599" ht="14.25" customHeight="1"/>
+    <row r="600" ht="14.25" customHeight="1"/>
+    <row r="601" ht="14.25" customHeight="1"/>
+    <row r="602" ht="14.25" customHeight="1"/>
+    <row r="603" ht="14.25" customHeight="1"/>
+    <row r="604" ht="14.25" customHeight="1"/>
+    <row r="605" ht="14.25" customHeight="1"/>
+    <row r="606" ht="14.25" customHeight="1"/>
+    <row r="607" ht="14.25" customHeight="1"/>
+    <row r="608" ht="14.25" customHeight="1"/>
+    <row r="609" ht="14.25" customHeight="1"/>
+    <row r="610" ht="14.25" customHeight="1"/>
+    <row r="611" ht="14.25" customHeight="1"/>
+    <row r="612" ht="14.25" customHeight="1"/>
+    <row r="613" ht="14.25" customHeight="1"/>
+    <row r="614" ht="14.25" customHeight="1"/>
+    <row r="615" ht="14.25" customHeight="1"/>
+    <row r="616" ht="14.25" customHeight="1"/>
+    <row r="617" ht="14.25" customHeight="1"/>
+    <row r="618" ht="14.25" customHeight="1"/>
+    <row r="619" ht="14.25" customHeight="1"/>
+    <row r="620" ht="14.25" customHeight="1"/>
+    <row r="621" ht="14.25" customHeight="1"/>
+    <row r="622" ht="14.25" customHeight="1"/>
+    <row r="623" ht="14.25" customHeight="1"/>
+    <row r="624" ht="14.25" customHeight="1"/>
+    <row r="625" ht="14.25" customHeight="1"/>
+    <row r="626" ht="14.25" customHeight="1"/>
+    <row r="627" ht="14.25" customHeight="1"/>
+    <row r="628" ht="14.25" customHeight="1"/>
+    <row r="629" ht="14.25" customHeight="1"/>
+    <row r="630" ht="14.25" customHeight="1"/>
+    <row r="631" ht="14.25" customHeight="1"/>
+    <row r="632" ht="14.25" customHeight="1"/>
+    <row r="633" ht="14.25" customHeight="1"/>
+    <row r="634" ht="14.25" customHeight="1"/>
+    <row r="635" ht="14.25" customHeight="1"/>
+    <row r="636" ht="14.25" customHeight="1"/>
+    <row r="637" ht="14.25" customHeight="1"/>
+    <row r="638" ht="14.25" customHeight="1"/>
+    <row r="639" ht="14.25" customHeight="1"/>
+    <row r="640" ht="14.25" customHeight="1"/>
+    <row r="641" ht="14.25" customHeight="1"/>
+    <row r="642" ht="14.25" customHeight="1"/>
+    <row r="643" ht="14.25" customHeight="1"/>
+    <row r="644" ht="14.25" customHeight="1"/>
+    <row r="645" ht="14.25" customHeight="1"/>
+    <row r="646" ht="14.25" customHeight="1"/>
+    <row r="647" ht="14.25" customHeight="1"/>
+    <row r="648" ht="14.25" customHeight="1"/>
+    <row r="649" ht="14.25" customHeight="1"/>
+    <row r="650" ht="14.25" customHeight="1"/>
+    <row r="651" ht="14.25" customHeight="1"/>
+    <row r="652" ht="14.25" customHeight="1"/>
+    <row r="653" ht="14.25" customHeight="1"/>
+    <row r="654" ht="14.25" customHeight="1"/>
+    <row r="655" ht="14.25" customHeight="1"/>
+    <row r="656" ht="14.25" customHeight="1"/>
+    <row r="657" ht="14.25" customHeight="1"/>
+    <row r="658" ht="14.25" customHeight="1"/>
+    <row r="659" ht="14.25" customHeight="1"/>
+    <row r="660" ht="14.25" customHeight="1"/>
+    <row r="661" ht="14.25" customHeight="1"/>
+    <row r="662" ht="14.25" customHeight="1"/>
+    <row r="663" ht="14.25" customHeight="1"/>
+    <row r="664" ht="14.25" customHeight="1"/>
+    <row r="665" ht="14.25" customHeight="1"/>
+    <row r="666" ht="14.25" customHeight="1"/>
+    <row r="667" ht="14.25" customHeight="1"/>
+    <row r="668" ht="14.25" customHeight="1"/>
+    <row r="669" ht="14.25" customHeight="1"/>
+    <row r="670" ht="14.25" customHeight="1"/>
+    <row r="671" ht="14.25" customHeight="1"/>
+    <row r="672" ht="14.25" customHeight="1"/>
+    <row r="673" ht="14.25" customHeight="1"/>
+    <row r="674" ht="14.25" customHeight="1"/>
+    <row r="675" ht="14.25" customHeight="1"/>
+    <row r="676" ht="14.25" customHeight="1"/>
+    <row r="677" ht="14.25" customHeight="1"/>
+    <row r="678" ht="14.25" customHeight="1"/>
+    <row r="679" ht="14.25" customHeight="1"/>
+    <row r="680" ht="14.25" customHeight="1"/>
+    <row r="681" ht="14.25" customHeight="1"/>
+    <row r="682" ht="14.25" customHeight="1"/>
+    <row r="683" ht="14.25" customHeight="1"/>
+    <row r="684" ht="14.25" customHeight="1"/>
+    <row r="685" ht="14.25" customHeight="1"/>
+    <row r="686" ht="14.25" customHeight="1"/>
+    <row r="687" ht="14.25" customHeight="1"/>
+    <row r="688" ht="14.25" customHeight="1"/>
+    <row r="689" ht="14.25" customHeight="1"/>
+    <row r="690" ht="14.25" customHeight="1"/>
+    <row r="691" ht="14.25" customHeight="1"/>
+    <row r="692" ht="14.25" customHeight="1"/>
+    <row r="693" ht="14.25" customHeight="1"/>
+    <row r="694" ht="14.25" customHeight="1"/>
+    <row r="695" ht="14.25" customHeight="1"/>
+    <row r="696" ht="14.25" customHeight="1"/>
+    <row r="697" ht="14.25" customHeight="1"/>
+    <row r="698" ht="14.25" customHeight="1"/>
+    <row r="699" ht="14.25" customHeight="1"/>
+    <row r="700" ht="14.25" customHeight="1"/>
+    <row r="701" ht="14.25" customHeight="1"/>
+    <row r="702" ht="14.25" customHeight="1"/>
+    <row r="703" ht="14.25" customHeight="1"/>
+    <row r="704" ht="14.25" customHeight="1"/>
+    <row r="705" ht="14.25" customHeight="1"/>
+    <row r="706" ht="14.25" customHeight="1"/>
+    <row r="707" ht="14.25" customHeight="1"/>
+    <row r="708" ht="14.25" customHeight="1"/>
+    <row r="709" ht="14.25" customHeight="1"/>
+    <row r="710" ht="14.25" customHeight="1"/>
+    <row r="711" ht="14.25" customHeight="1"/>
+    <row r="712" ht="14.25" customHeight="1"/>
+    <row r="713" ht="14.25" customHeight="1"/>
+    <row r="714" ht="14.25" customHeight="1"/>
+    <row r="715" ht="14.25" customHeight="1"/>
+    <row r="716" ht="14.25" customHeight="1"/>
+    <row r="717" ht="14.25" customHeight="1"/>
+    <row r="718" ht="14.25" customHeight="1"/>
+    <row r="719" ht="14.25" customHeight="1"/>
+    <row r="720" ht="14.25" customHeight="1"/>
+    <row r="721" ht="14.25" customHeight="1"/>
+    <row r="722" ht="14.25" customHeight="1"/>
+    <row r="723" ht="14.25" customHeight="1"/>
+    <row r="724" ht="14.25" customHeight="1"/>
+    <row r="725" ht="14.25" customHeight="1"/>
+    <row r="726" ht="14.25" customHeight="1"/>
+    <row r="727" ht="14.25" customHeight="1"/>
+    <row r="728" ht="14.25" customHeight="1"/>
+    <row r="729" ht="14.25" customHeight="1"/>
+    <row r="730" ht="14.25" customHeight="1"/>
+    <row r="731" ht="14.25" customHeight="1"/>
+    <row r="732" ht="14.25" customHeight="1"/>
+    <row r="733" ht="14.25" customHeight="1"/>
+    <row r="734" ht="14.25" customHeight="1"/>
+    <row r="735" ht="14.25" customHeight="1"/>
+    <row r="736" ht="14.25" customHeight="1"/>
+    <row r="737" ht="14.25" customHeight="1"/>
+    <row r="738" ht="14.25" customHeight="1"/>
+    <row r="739" ht="14.25" customHeight="1"/>
+    <row r="740" ht="14.25" customHeight="1"/>
+    <row r="741" ht="14.25" customHeight="1"/>
+    <row r="742" ht="14.25" customHeight="1"/>
+    <row r="743" ht="14.25" customHeight="1"/>
+    <row r="744" ht="14.25" customHeight="1"/>
+    <row r="745" ht="14.25" customHeight="1"/>
+    <row r="746" ht="14.25" customHeight="1"/>
+    <row r="747" ht="14.25" customHeight="1"/>
+    <row r="748" ht="14.25" customHeight="1"/>
+    <row r="749" ht="14.25" customHeight="1"/>
+    <row r="750" ht="14.25" customHeight="1"/>
+    <row r="751" ht="14.25" customHeight="1"/>
+    <row r="752" ht="14.25" customHeight="1"/>
+    <row r="753" ht="14.25" customHeight="1"/>
+    <row r="754" ht="14.25" customHeight="1"/>
+    <row r="755" ht="14.25" customHeight="1"/>
+    <row r="756" ht="14.25" customHeight="1"/>
+    <row r="757" ht="14.25" customHeight="1"/>
+    <row r="758" ht="14.25" customHeight="1"/>
+    <row r="759" ht="14.25" customHeight="1"/>
+    <row r="760" ht="14.25" customHeight="1"/>
+    <row r="761" ht="14.25" customHeight="1"/>
+    <row r="762" ht="14.25" customHeight="1"/>
+    <row r="763" ht="14.25" customHeight="1"/>
+    <row r="764" ht="14.25" customHeight="1"/>
+    <row r="765" ht="14.25" customHeight="1"/>
+    <row r="766" ht="14.25" customHeight="1"/>
+    <row r="767" ht="14.25" customHeight="1"/>
+    <row r="768" ht="14.25" customHeight="1"/>
+    <row r="769" ht="14.25" customHeight="1"/>
+    <row r="770" ht="14.25" customHeight="1"/>
+    <row r="771" ht="14.25" customHeight="1"/>
+    <row r="772" ht="14.25" customHeight="1"/>
+    <row r="773" ht="14.25" customHeight="1"/>
+    <row r="774" ht="14.25" customHeight="1"/>
+    <row r="775" ht="14.25" customHeight="1"/>
+    <row r="776" ht="14.25" customHeight="1"/>
+    <row r="777" ht="14.25" customHeight="1"/>
+    <row r="778" ht="14.25" customHeight="1"/>
+    <row r="779" ht="14.25" customHeight="1"/>
+    <row r="780" ht="14.25" customHeight="1"/>
+    <row r="781" ht="14.25" customHeight="1"/>
+    <row r="782" ht="14.25" customHeight="1"/>
+    <row r="783" ht="14.25" customHeight="1"/>
+    <row r="784" ht="14.25" customHeight="1"/>
+    <row r="785" ht="14.25" customHeight="1"/>
+    <row r="786" ht="14.25" customHeight="1"/>
+    <row r="787" ht="14.25" customHeight="1"/>
+    <row r="788" ht="14.25" customHeight="1"/>
+    <row r="789" ht="14.25" customHeight="1"/>
+    <row r="790" ht="14.25" customHeight="1"/>
+    <row r="791" ht="14.25" customHeight="1"/>
+    <row r="792" ht="14.25" customHeight="1"/>
+    <row r="793" ht="14.25" customHeight="1"/>
+    <row r="794" ht="14.25" customHeight="1"/>
+    <row r="795" ht="14.25" customHeight="1"/>
+    <row r="796" ht="14.25" customHeight="1"/>
+    <row r="797" ht="14.25" customHeight="1"/>
+    <row r="798" ht="14.25" customHeight="1"/>
+    <row r="799" ht="14.25" customHeight="1"/>
+    <row r="800" ht="14.25" customHeight="1"/>
+    <row r="801" ht="14.25" customHeight="1"/>
+    <row r="802" ht="14.25" customHeight="1"/>
+    <row r="803" ht="14.25" customHeight="1"/>
+    <row r="804" ht="14.25" customHeight="1"/>
+    <row r="805" ht="14.25" customHeight="1"/>
+    <row r="806" ht="14.25" customHeight="1"/>
+    <row r="807" ht="14.25" customHeight="1"/>
+    <row r="808" ht="14.25" customHeight="1"/>
+    <row r="809" ht="14.25" customHeight="1"/>
+    <row r="810" ht="14.25" customHeight="1"/>
+    <row r="811" ht="14.25" customHeight="1"/>
+    <row r="812" ht="14.25" customHeight="1"/>
+    <row r="813" ht="14.25" customHeight="1"/>
+    <row r="814" ht="14.25" customHeight="1"/>
+    <row r="815" ht="14.25" customHeight="1"/>
+    <row r="816" ht="14.25" customHeight="1"/>
+    <row r="817" ht="14.25" customHeight="1"/>
+    <row r="818" ht="14.25" customHeight="1"/>
+    <row r="819" ht="14.25" customHeight="1"/>
+    <row r="820" ht="14.25" customHeight="1"/>
+    <row r="821" ht="14.25" customHeight="1"/>
+    <row r="822" ht="14.25" customHeight="1"/>
+    <row r="823" ht="14.25" customHeight="1"/>
+    <row r="824" ht="14.25" customHeight="1"/>
+    <row r="825" ht="14.25" customHeight="1"/>
+    <row r="826" ht="14.25" customHeight="1"/>
+    <row r="827" ht="14.25" customHeight="1"/>
+    <row r="828" ht="14.25" customHeight="1"/>
+    <row r="829" ht="14.25" customHeight="1"/>
+    <row r="830" ht="14.25" customHeight="1"/>
+    <row r="831" ht="14.25" customHeight="1"/>
+    <row r="832" ht="14.25" customHeight="1"/>
+    <row r="833" ht="14.25" customHeight="1"/>
+    <row r="834" ht="14.25" customHeight="1"/>
+    <row r="835" ht="14.25" customHeight="1"/>
+    <row r="836" ht="14.25" customHeight="1"/>
+    <row r="837" ht="14.25" customHeight="1"/>
+    <row r="838" ht="14.25" customHeight="1"/>
+    <row r="839" ht="14.25" customHeight="1"/>
+    <row r="840" ht="14.25" customHeight="1"/>
+    <row r="841" ht="14.25" customHeight="1"/>
+    <row r="842" ht="14.25" customHeight="1"/>
+    <row r="843" ht="14.25" customHeight="1"/>
+    <row r="844" ht="14.25" customHeight="1"/>
+    <row r="845" ht="14.25" customHeight="1"/>
+    <row r="846" ht="14.25" customHeight="1"/>
+    <row r="847" ht="14.25" customHeight="1"/>
+    <row r="848" ht="14.25" customHeight="1"/>
+    <row r="849" ht="14.25" customHeight="1"/>
+    <row r="850" ht="14.25" customHeight="1"/>
+    <row r="851" ht="14.25" customHeight="1"/>
+    <row r="852" ht="14.25" customHeight="1"/>
+    <row r="853" ht="14.25" customHeight="1"/>
+    <row r="854" ht="14.25" customHeight="1"/>
+    <row r="855" ht="14.25" customHeight="1"/>
+    <row r="856" ht="14.25" customHeight="1"/>
+    <row r="857" ht="14.25" customHeight="1"/>
+    <row r="858" ht="14.25" customHeight="1"/>
+    <row r="859" ht="14.25" customHeight="1"/>
+    <row r="860" ht="14.25" customHeight="1"/>
+    <row r="861" ht="14.25" customHeight="1"/>
+    <row r="862" ht="14.25" customHeight="1"/>
+    <row r="863" ht="14.25" customHeight="1"/>
+    <row r="864" ht="14.25" customHeight="1"/>
+    <row r="865" ht="14.25" customHeight="1"/>
+    <row r="866" ht="14.25" customHeight="1"/>
+    <row r="867" ht="14.25" customHeight="1"/>
+    <row r="868" ht="14.25" customHeight="1"/>
+    <row r="869" ht="14.25" customHeight="1"/>
+    <row r="870" ht="14.25" customHeight="1"/>
+    <row r="871" ht="14.25" customHeight="1"/>
+    <row r="872" ht="14.25" customHeight="1"/>
+    <row r="873" ht="14.25" customHeight="1"/>
+    <row r="874" ht="14.25" customHeight="1"/>
+    <row r="875" ht="14.25" customHeight="1"/>
+    <row r="876" ht="14.25" customHeight="1"/>
+    <row r="877" ht="14.25" customHeight="1"/>
+    <row r="878" ht="14.25" customHeight="1"/>
+    <row r="879" ht="14.25" customHeight="1"/>
+    <row r="880" ht="14.25" customHeight="1"/>
+    <row r="881" ht="14.25" customHeight="1"/>
+    <row r="882" ht="14.25" customHeight="1"/>
+    <row r="883" ht="14.25" customHeight="1"/>
+    <row r="884" ht="14.25" customHeight="1"/>
+    <row r="885" ht="14.25" customHeight="1"/>
+    <row r="886" ht="14.25" customHeight="1"/>
+    <row r="887" ht="14.25" customHeight="1"/>
+    <row r="888" ht="14.25" customHeight="1"/>
+    <row r="889" ht="14.25" customHeight="1"/>
+    <row r="890" ht="14.25" customHeight="1"/>
+    <row r="891" ht="14.25" customHeight="1"/>
+    <row r="892" ht="14.25" customHeight="1"/>
+    <row r="893" ht="14.25" customHeight="1"/>
+    <row r="894" ht="14.25" customHeight="1"/>
+    <row r="895" ht="14.25" customHeight="1"/>
+    <row r="896" ht="14.25" customHeight="1"/>
+    <row r="897" ht="14.25" customHeight="1"/>
+    <row r="898" ht="14.25" customHeight="1"/>
+    <row r="899" ht="14.25" customHeight="1"/>
+    <row r="900" ht="14.25" customHeight="1"/>
+    <row r="901" ht="14.25" customHeight="1"/>
+    <row r="902" ht="14.25" customHeight="1"/>
+    <row r="903" ht="14.25" customHeight="1"/>
+    <row r="904" ht="14.25" customHeight="1"/>
+    <row r="905" ht="14.25" customHeight="1"/>
+    <row r="906" ht="14.25" customHeight="1"/>
+    <row r="907" ht="14.25" customHeight="1"/>
+    <row r="908" ht="14.25" customHeight="1"/>
+    <row r="909" ht="14.25" customHeight="1"/>
+    <row r="910" ht="14.25" customHeight="1"/>
+    <row r="911" ht="14.25" customHeight="1"/>
+    <row r="912" ht="14.25" customHeight="1"/>
+    <row r="913" ht="14.25" customHeight="1"/>
+    <row r="914" ht="14.25" customHeight="1"/>
+    <row r="915" ht="14.25" customHeight="1"/>
+    <row r="916" ht="14.25" customHeight="1"/>
+    <row r="917" ht="14.25" customHeight="1"/>
+    <row r="918" ht="14.25" customHeight="1"/>
+    <row r="919" ht="14.25" customHeight="1"/>
+    <row r="920" ht="14.25" customHeight="1"/>
+    <row r="921" ht="14.25" customHeight="1"/>
+    <row r="922" ht="14.25" customHeight="1"/>
+    <row r="923" ht="14.25" customHeight="1"/>
+    <row r="924" ht="14.25" customHeight="1"/>
+    <row r="925" ht="14.25" customHeight="1"/>
+    <row r="926" ht="14.25" customHeight="1"/>
+    <row r="927" ht="14.25" customHeight="1"/>
+    <row r="928" ht="14.25" customHeight="1"/>
+    <row r="929" ht="14.25" customHeight="1"/>
+    <row r="930" ht="14.25" customHeight="1"/>
+    <row r="931" ht="14.25" customHeight="1"/>
+    <row r="932" ht="14.25" customHeight="1"/>
+    <row r="933" ht="14.25" customHeight="1"/>
+    <row r="934" ht="14.25" customHeight="1"/>
+    <row r="935" ht="14.25" customHeight="1"/>
+    <row r="936" ht="14.25" customHeight="1"/>
+    <row r="937" ht="14.25" customHeight="1"/>
+    <row r="938" ht="14.25" customHeight="1"/>
+    <row r="939" ht="14.25" customHeight="1"/>
+    <row r="940" ht="14.25" customHeight="1"/>
+    <row r="941" ht="14.25" customHeight="1"/>
+    <row r="942" ht="14.25" customHeight="1"/>
+    <row r="943" ht="14.25" customHeight="1"/>
+    <row r="944" ht="14.25" customHeight="1"/>
+    <row r="945" ht="14.25" customHeight="1"/>
+    <row r="946" ht="14.25" customHeight="1"/>
+    <row r="947" ht="14.25" customHeight="1"/>
+    <row r="948" ht="14.25" customHeight="1"/>
+    <row r="949" ht="14.25" customHeight="1"/>
+    <row r="950" ht="14.25" customHeight="1"/>
+    <row r="951" ht="14.25" customHeight="1"/>
+    <row r="952" ht="14.25" customHeight="1"/>
+    <row r="953" ht="14.25" customHeight="1"/>
+    <row r="954" ht="14.25" customHeight="1"/>
+    <row r="955" ht="14.25" customHeight="1"/>
+    <row r="956" ht="14.25" customHeight="1"/>
+    <row r="957" ht="14.25" customHeight="1"/>
+    <row r="958" ht="14.25" customHeight="1"/>
+    <row r="959" ht="14.25" customHeight="1"/>
+    <row r="960" ht="14.25" customHeight="1"/>
+    <row r="961" ht="14.25" customHeight="1"/>
+    <row r="962" ht="14.25" customHeight="1"/>
+    <row r="963" ht="14.25" customHeight="1"/>
+    <row r="964" ht="14.25" customHeight="1"/>
+    <row r="965" ht="14.25" customHeight="1"/>
+    <row r="966" ht="14.25" customHeight="1"/>
+    <row r="967" ht="14.25" customHeight="1"/>
+    <row r="968" ht="14.25" customHeight="1"/>
+    <row r="969" ht="14.25" customHeight="1"/>
+    <row r="970" ht="14.25" customHeight="1"/>
+    <row r="971" ht="14.25" customHeight="1"/>
+    <row r="972" ht="14.25" customHeight="1"/>
+    <row r="973" ht="14.25" customHeight="1"/>
+    <row r="974" ht="14.25" customHeight="1"/>
+    <row r="975" ht="14.25" customHeight="1"/>
+    <row r="976" ht="14.25" customHeight="1"/>
+    <row r="977" ht="14.25" customHeight="1"/>
+    <row r="978" ht="14.25" customHeight="1"/>
+    <row r="979" ht="14.25" customHeight="1"/>
+    <row r="980" ht="14.25" customHeight="1"/>
+    <row r="981" ht="14.25" customHeight="1"/>
+    <row r="982" ht="14.25" customHeight="1"/>
+    <row r="983" ht="14.25" customHeight="1"/>
+    <row r="984" ht="14.25" customHeight="1"/>
+    <row r="985" ht="14.25" customHeight="1"/>
+    <row r="986" ht="14.25" customHeight="1"/>
+    <row r="987" ht="14.25" customHeight="1"/>
+    <row r="988" ht="14.25" customHeight="1"/>
+    <row r="989" ht="14.25" customHeight="1"/>
+    <row r="990" ht="14.25" customHeight="1"/>
+    <row r="991" ht="14.25" customHeight="1"/>
+    <row r="992" ht="14.25" customHeight="1"/>
+    <row r="993" ht="14.25" customHeight="1"/>
+    <row r="994" ht="14.25" customHeight="1"/>
+    <row r="995" ht="14.25" customHeight="1"/>
+    <row r="996" ht="14.25" customHeight="1"/>
+    <row r="997" ht="14.25" customHeight="1"/>
+    <row r="998" ht="14.25" customHeight="1"/>
+    <row r="999" ht="14.25" customHeight="1"/>
+    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="K5:L5"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="E7:G7"/>
     <mergeCell ref="I7:L7"/>
     <mergeCell ref="A17:L17"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="K4:L4"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FF16A34A"/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C1000"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="4" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-    </row>
-    <row r="3" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="36" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="B15" s="36" t="s">
-        <v>141</v>
-      </c>
-      <c r="C15" s="36" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="B16" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="B17" s="40" t="s">
-        <v>147</v>
-      </c>
-      <c r="C17" s="40" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="B18" s="40" t="s">
-        <v>149</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="B19" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="C19" s="40" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="B20" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="C20" s="40" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="B21" s="42" t="s">
-        <v>156</v>
-      </c>
-      <c r="C21" s="42" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="B22" s="42" t="s">
-        <v>158</v>
-      </c>
-      <c r="C22" s="42" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="B23" s="42" t="s">
-        <v>160</v>
-      </c>
-      <c r="C23" s="42" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="B24" s="42" t="s">
-        <v>162</v>
-      </c>
-      <c r="C24" s="42" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="B25" s="42" t="s">
-        <v>164</v>
-      </c>
-      <c r="C25" s="42" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="B26" s="44" t="s">
-        <v>147</v>
-      </c>
-      <c r="C26" s="44" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="B27" s="44" t="s">
-        <v>168</v>
-      </c>
-      <c r="C27" s="44" t="s">
-        <v>169</v>
-      </c>
-    </row>
+    <row r="1" spans="1:3" ht="36" customHeight="1">
+      <c r="A1" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="42"/>
+    </row>
+    <row r="2" spans="1:3" ht="21.75" customHeight="1">
+      <c r="A2" s="43" t="s">
+        <v>200</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="42"/>
+    </row>
+    <row r="3" spans="1:3" ht="36" customHeight="1">
+      <c r="A3" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="36" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="36" customHeight="1">
+      <c r="A6" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="36" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="36" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="36" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="36" customHeight="1">
+      <c r="A10" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="36" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="13" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="14" spans="1:3" ht="27.75" customHeight="1">
+      <c r="A14" s="51" t="s">
+        <v>228</v>
+      </c>
+      <c r="B14" s="41"/>
+      <c r="C14" s="42"/>
+    </row>
+    <row r="15" spans="1:3" ht="24" customHeight="1">
+      <c r="A15" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="24" customHeight="1">
+      <c r="A16" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="24" customHeight="1">
+      <c r="A17" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="24" customHeight="1">
+      <c r="A18" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="24" customHeight="1">
+      <c r="A19" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="24" customHeight="1">
+      <c r="A20" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="24" customHeight="1">
+      <c r="A21" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="B21" s="37" t="s">
+        <v>245</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="24" customHeight="1">
+      <c r="A22" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="24" customHeight="1">
+      <c r="A23" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="24" customHeight="1">
+      <c r="A24" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="C24" s="37" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="24" customHeight="1">
+      <c r="A25" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="B25" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="24" customHeight="1">
+      <c r="A26" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="B26" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="24" customHeight="1">
+      <c r="A27" s="38" t="s">
+        <v>255</v>
+      </c>
+      <c r="B27" s="39" t="s">
+        <v>257</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="31" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:3" ht="14.25" customHeight="1"/>
+    <row r="33" ht="14.25" customHeight="1"/>
+    <row r="34" ht="14.25" customHeight="1"/>
+    <row r="35" ht="14.25" customHeight="1"/>
+    <row r="36" ht="14.25" customHeight="1"/>
+    <row r="37" ht="14.25" customHeight="1"/>
+    <row r="38" ht="14.25" customHeight="1"/>
+    <row r="39" ht="14.25" customHeight="1"/>
+    <row r="40" ht="14.25" customHeight="1"/>
+    <row r="41" ht="14.25" customHeight="1"/>
+    <row r="42" ht="14.25" customHeight="1"/>
+    <row r="43" ht="14.25" customHeight="1"/>
+    <row r="44" ht="14.25" customHeight="1"/>
+    <row r="45" ht="14.25" customHeight="1"/>
+    <row r="46" ht="14.25" customHeight="1"/>
+    <row r="47" ht="14.25" customHeight="1"/>
+    <row r="48" ht="14.25" customHeight="1"/>
+    <row r="49" ht="14.25" customHeight="1"/>
+    <row r="50" ht="14.25" customHeight="1"/>
+    <row r="51" ht="14.25" customHeight="1"/>
+    <row r="52" ht="14.25" customHeight="1"/>
+    <row r="53" ht="14.25" customHeight="1"/>
+    <row r="54" ht="14.25" customHeight="1"/>
+    <row r="55" ht="14.25" customHeight="1"/>
+    <row r="56" ht="14.25" customHeight="1"/>
+    <row r="57" ht="14.25" customHeight="1"/>
+    <row r="58" ht="14.25" customHeight="1"/>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
+    <row r="74" ht="14.25" customHeight="1"/>
+    <row r="75" ht="14.25" customHeight="1"/>
+    <row r="76" ht="14.25" customHeight="1"/>
+    <row r="77" ht="14.25" customHeight="1"/>
+    <row r="78" ht="14.25" customHeight="1"/>
+    <row r="79" ht="14.25" customHeight="1"/>
+    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="81" ht="14.25" customHeight="1"/>
+    <row r="82" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1"/>
+    <row r="85" ht="14.25" customHeight="1"/>
+    <row r="86" ht="14.25" customHeight="1"/>
+    <row r="87" ht="14.25" customHeight="1"/>
+    <row r="88" ht="14.25" customHeight="1"/>
+    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
+    <row r="95" ht="14.25" customHeight="1"/>
+    <row r="96" ht="14.25" customHeight="1"/>
+    <row r="97" ht="14.25" customHeight="1"/>
+    <row r="98" ht="14.25" customHeight="1"/>
+    <row r="99" ht="14.25" customHeight="1"/>
+    <row r="100" ht="14.25" customHeight="1"/>
+    <row r="101" ht="14.25" customHeight="1"/>
+    <row r="102" ht="14.25" customHeight="1"/>
+    <row r="103" ht="14.25" customHeight="1"/>
+    <row r="104" ht="14.25" customHeight="1"/>
+    <row r="105" ht="14.25" customHeight="1"/>
+    <row r="106" ht="14.25" customHeight="1"/>
+    <row r="107" ht="14.25" customHeight="1"/>
+    <row r="108" ht="14.25" customHeight="1"/>
+    <row r="109" ht="14.25" customHeight="1"/>
+    <row r="110" ht="14.25" customHeight="1"/>
+    <row r="111" ht="14.25" customHeight="1"/>
+    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="113" ht="14.25" customHeight="1"/>
+    <row r="114" ht="14.25" customHeight="1"/>
+    <row r="115" ht="14.25" customHeight="1"/>
+    <row r="116" ht="14.25" customHeight="1"/>
+    <row r="117" ht="14.25" customHeight="1"/>
+    <row r="118" ht="14.25" customHeight="1"/>
+    <row r="119" ht="14.25" customHeight="1"/>
+    <row r="120" ht="14.25" customHeight="1"/>
+    <row r="121" ht="14.25" customHeight="1"/>
+    <row r="122" ht="14.25" customHeight="1"/>
+    <row r="123" ht="14.25" customHeight="1"/>
+    <row r="124" ht="14.25" customHeight="1"/>
+    <row r="125" ht="14.25" customHeight="1"/>
+    <row r="126" ht="14.25" customHeight="1"/>
+    <row r="127" ht="14.25" customHeight="1"/>
+    <row r="128" ht="14.25" customHeight="1"/>
+    <row r="129" ht="14.25" customHeight="1"/>
+    <row r="130" ht="14.25" customHeight="1"/>
+    <row r="131" ht="14.25" customHeight="1"/>
+    <row r="132" ht="14.25" customHeight="1"/>
+    <row r="133" ht="14.25" customHeight="1"/>
+    <row r="134" ht="14.25" customHeight="1"/>
+    <row r="135" ht="14.25" customHeight="1"/>
+    <row r="136" ht="14.25" customHeight="1"/>
+    <row r="137" ht="14.25" customHeight="1"/>
+    <row r="138" ht="14.25" customHeight="1"/>
+    <row r="139" ht="14.25" customHeight="1"/>
+    <row r="140" ht="14.25" customHeight="1"/>
+    <row r="141" ht="14.25" customHeight="1"/>
+    <row r="142" ht="14.25" customHeight="1"/>
+    <row r="143" ht="14.25" customHeight="1"/>
+    <row r="144" ht="14.25" customHeight="1"/>
+    <row r="145" ht="14.25" customHeight="1"/>
+    <row r="146" ht="14.25" customHeight="1"/>
+    <row r="147" ht="14.25" customHeight="1"/>
+    <row r="148" ht="14.25" customHeight="1"/>
+    <row r="149" ht="14.25" customHeight="1"/>
+    <row r="150" ht="14.25" customHeight="1"/>
+    <row r="151" ht="14.25" customHeight="1"/>
+    <row r="152" ht="14.25" customHeight="1"/>
+    <row r="153" ht="14.25" customHeight="1"/>
+    <row r="154" ht="14.25" customHeight="1"/>
+    <row r="155" ht="14.25" customHeight="1"/>
+    <row r="156" ht="14.25" customHeight="1"/>
+    <row r="157" ht="14.25" customHeight="1"/>
+    <row r="158" ht="14.25" customHeight="1"/>
+    <row r="159" ht="14.25" customHeight="1"/>
+    <row r="160" ht="14.25" customHeight="1"/>
+    <row r="161" ht="14.25" customHeight="1"/>
+    <row r="162" ht="14.25" customHeight="1"/>
+    <row r="163" ht="14.25" customHeight="1"/>
+    <row r="164" ht="14.25" customHeight="1"/>
+    <row r="165" ht="14.25" customHeight="1"/>
+    <row r="166" ht="14.25" customHeight="1"/>
+    <row r="167" ht="14.25" customHeight="1"/>
+    <row r="168" ht="14.25" customHeight="1"/>
+    <row r="169" ht="14.25" customHeight="1"/>
+    <row r="170" ht="14.25" customHeight="1"/>
+    <row r="171" ht="14.25" customHeight="1"/>
+    <row r="172" ht="14.25" customHeight="1"/>
+    <row r="173" ht="14.25" customHeight="1"/>
+    <row r="174" ht="14.25" customHeight="1"/>
+    <row r="175" ht="14.25" customHeight="1"/>
+    <row r="176" ht="14.25" customHeight="1"/>
+    <row r="177" ht="14.25" customHeight="1"/>
+    <row r="178" ht="14.25" customHeight="1"/>
+    <row r="179" ht="14.25" customHeight="1"/>
+    <row r="180" ht="14.25" customHeight="1"/>
+    <row r="181" ht="14.25" customHeight="1"/>
+    <row r="182" ht="14.25" customHeight="1"/>
+    <row r="183" ht="14.25" customHeight="1"/>
+    <row r="184" ht="14.25" customHeight="1"/>
+    <row r="185" ht="14.25" customHeight="1"/>
+    <row r="186" ht="14.25" customHeight="1"/>
+    <row r="187" ht="14.25" customHeight="1"/>
+    <row r="188" ht="14.25" customHeight="1"/>
+    <row r="189" ht="14.25" customHeight="1"/>
+    <row r="190" ht="14.25" customHeight="1"/>
+    <row r="191" ht="14.25" customHeight="1"/>
+    <row r="192" ht="14.25" customHeight="1"/>
+    <row r="193" ht="14.25" customHeight="1"/>
+    <row r="194" ht="14.25" customHeight="1"/>
+    <row r="195" ht="14.25" customHeight="1"/>
+    <row r="196" ht="14.25" customHeight="1"/>
+    <row r="197" ht="14.25" customHeight="1"/>
+    <row r="198" ht="14.25" customHeight="1"/>
+    <row r="199" ht="14.25" customHeight="1"/>
+    <row r="200" ht="14.25" customHeight="1"/>
+    <row r="201" ht="14.25" customHeight="1"/>
+    <row r="202" ht="14.25" customHeight="1"/>
+    <row r="203" ht="14.25" customHeight="1"/>
+    <row r="204" ht="14.25" customHeight="1"/>
+    <row r="205" ht="14.25" customHeight="1"/>
+    <row r="206" ht="14.25" customHeight="1"/>
+    <row r="207" ht="14.25" customHeight="1"/>
+    <row r="208" ht="14.25" customHeight="1"/>
+    <row r="209" ht="14.25" customHeight="1"/>
+    <row r="210" ht="14.25" customHeight="1"/>
+    <row r="211" ht="14.25" customHeight="1"/>
+    <row r="212" ht="14.25" customHeight="1"/>
+    <row r="213" ht="14.25" customHeight="1"/>
+    <row r="214" ht="14.25" customHeight="1"/>
+    <row r="215" ht="14.25" customHeight="1"/>
+    <row r="216" ht="14.25" customHeight="1"/>
+    <row r="217" ht="14.25" customHeight="1"/>
+    <row r="218" ht="14.25" customHeight="1"/>
+    <row r="219" ht="14.25" customHeight="1"/>
+    <row r="220" ht="14.25" customHeight="1"/>
+    <row r="221" ht="14.25" customHeight="1"/>
+    <row r="222" ht="14.25" customHeight="1"/>
+    <row r="223" ht="14.25" customHeight="1"/>
+    <row r="224" ht="14.25" customHeight="1"/>
+    <row r="225" ht="14.25" customHeight="1"/>
+    <row r="226" ht="14.25" customHeight="1"/>
+    <row r="227" ht="14.25" customHeight="1"/>
+    <row r="228" ht="14.25" customHeight="1"/>
+    <row r="229" ht="14.25" customHeight="1"/>
+    <row r="230" ht="14.25" customHeight="1"/>
+    <row r="231" ht="14.25" customHeight="1"/>
+    <row r="232" ht="14.25" customHeight="1"/>
+    <row r="233" ht="14.25" customHeight="1"/>
+    <row r="234" ht="14.25" customHeight="1"/>
+    <row r="235" ht="14.25" customHeight="1"/>
+    <row r="236" ht="14.25" customHeight="1"/>
+    <row r="237" ht="14.25" customHeight="1"/>
+    <row r="238" ht="14.25" customHeight="1"/>
+    <row r="239" ht="14.25" customHeight="1"/>
+    <row r="240" ht="14.25" customHeight="1"/>
+    <row r="241" ht="14.25" customHeight="1"/>
+    <row r="242" ht="14.25" customHeight="1"/>
+    <row r="243" ht="14.25" customHeight="1"/>
+    <row r="244" ht="14.25" customHeight="1"/>
+    <row r="245" ht="14.25" customHeight="1"/>
+    <row r="246" ht="14.25" customHeight="1"/>
+    <row r="247" ht="14.25" customHeight="1"/>
+    <row r="248" ht="14.25" customHeight="1"/>
+    <row r="249" ht="14.25" customHeight="1"/>
+    <row r="250" ht="14.25" customHeight="1"/>
+    <row r="251" ht="14.25" customHeight="1"/>
+    <row r="252" ht="14.25" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
+    <row r="254" ht="14.25" customHeight="1"/>
+    <row r="255" ht="14.25" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
+    <row r="257" ht="14.25" customHeight="1"/>
+    <row r="258" ht="14.25" customHeight="1"/>
+    <row r="259" ht="14.25" customHeight="1"/>
+    <row r="260" ht="14.25" customHeight="1"/>
+    <row r="261" ht="14.25" customHeight="1"/>
+    <row r="262" ht="14.25" customHeight="1"/>
+    <row r="263" ht="14.25" customHeight="1"/>
+    <row r="264" ht="14.25" customHeight="1"/>
+    <row r="265" ht="14.25" customHeight="1"/>
+    <row r="266" ht="14.25" customHeight="1"/>
+    <row r="267" ht="14.25" customHeight="1"/>
+    <row r="268" ht="14.25" customHeight="1"/>
+    <row r="269" ht="14.25" customHeight="1"/>
+    <row r="270" ht="14.25" customHeight="1"/>
+    <row r="271" ht="14.25" customHeight="1"/>
+    <row r="272" ht="14.25" customHeight="1"/>
+    <row r="273" ht="14.25" customHeight="1"/>
+    <row r="274" ht="14.25" customHeight="1"/>
+    <row r="275" ht="14.25" customHeight="1"/>
+    <row r="276" ht="14.25" customHeight="1"/>
+    <row r="277" ht="14.25" customHeight="1"/>
+    <row r="278" ht="14.25" customHeight="1"/>
+    <row r="279" ht="14.25" customHeight="1"/>
+    <row r="280" ht="14.25" customHeight="1"/>
+    <row r="281" ht="14.25" customHeight="1"/>
+    <row r="282" ht="14.25" customHeight="1"/>
+    <row r="283" ht="14.25" customHeight="1"/>
+    <row r="284" ht="14.25" customHeight="1"/>
+    <row r="285" ht="14.25" customHeight="1"/>
+    <row r="286" ht="14.25" customHeight="1"/>
+    <row r="287" ht="14.25" customHeight="1"/>
+    <row r="288" ht="14.25" customHeight="1"/>
+    <row r="289" ht="14.25" customHeight="1"/>
+    <row r="290" ht="14.25" customHeight="1"/>
+    <row r="291" ht="14.25" customHeight="1"/>
+    <row r="292" ht="14.25" customHeight="1"/>
+    <row r="293" ht="14.25" customHeight="1"/>
+    <row r="294" ht="14.25" customHeight="1"/>
+    <row r="295" ht="14.25" customHeight="1"/>
+    <row r="296" ht="14.25" customHeight="1"/>
+    <row r="297" ht="14.25" customHeight="1"/>
+    <row r="298" ht="14.25" customHeight="1"/>
+    <row r="299" ht="14.25" customHeight="1"/>
+    <row r="300" ht="14.25" customHeight="1"/>
+    <row r="301" ht="14.25" customHeight="1"/>
+    <row r="302" ht="14.25" customHeight="1"/>
+    <row r="303" ht="14.25" customHeight="1"/>
+    <row r="304" ht="14.25" customHeight="1"/>
+    <row r="305" ht="14.25" customHeight="1"/>
+    <row r="306" ht="14.25" customHeight="1"/>
+    <row r="307" ht="14.25" customHeight="1"/>
+    <row r="308" ht="14.25" customHeight="1"/>
+    <row r="309" ht="14.25" customHeight="1"/>
+    <row r="310" ht="14.25" customHeight="1"/>
+    <row r="311" ht="14.25" customHeight="1"/>
+    <row r="312" ht="14.25" customHeight="1"/>
+    <row r="313" ht="14.25" customHeight="1"/>
+    <row r="314" ht="14.25" customHeight="1"/>
+    <row r="315" ht="14.25" customHeight="1"/>
+    <row r="316" ht="14.25" customHeight="1"/>
+    <row r="317" ht="14.25" customHeight="1"/>
+    <row r="318" ht="14.25" customHeight="1"/>
+    <row r="319" ht="14.25" customHeight="1"/>
+    <row r="320" ht="14.25" customHeight="1"/>
+    <row r="321" ht="14.25" customHeight="1"/>
+    <row r="322" ht="14.25" customHeight="1"/>
+    <row r="323" ht="14.25" customHeight="1"/>
+    <row r="324" ht="14.25" customHeight="1"/>
+    <row r="325" ht="14.25" customHeight="1"/>
+    <row r="326" ht="14.25" customHeight="1"/>
+    <row r="327" ht="14.25" customHeight="1"/>
+    <row r="328" ht="14.25" customHeight="1"/>
+    <row r="329" ht="14.25" customHeight="1"/>
+    <row r="330" ht="14.25" customHeight="1"/>
+    <row r="331" ht="14.25" customHeight="1"/>
+    <row r="332" ht="14.25" customHeight="1"/>
+    <row r="333" ht="14.25" customHeight="1"/>
+    <row r="334" ht="14.25" customHeight="1"/>
+    <row r="335" ht="14.25" customHeight="1"/>
+    <row r="336" ht="14.25" customHeight="1"/>
+    <row r="337" ht="14.25" customHeight="1"/>
+    <row r="338" ht="14.25" customHeight="1"/>
+    <row r="339" ht="14.25" customHeight="1"/>
+    <row r="340" ht="14.25" customHeight="1"/>
+    <row r="341" ht="14.25" customHeight="1"/>
+    <row r="342" ht="14.25" customHeight="1"/>
+    <row r="343" ht="14.25" customHeight="1"/>
+    <row r="344" ht="14.25" customHeight="1"/>
+    <row r="345" ht="14.25" customHeight="1"/>
+    <row r="346" ht="14.25" customHeight="1"/>
+    <row r="347" ht="14.25" customHeight="1"/>
+    <row r="348" ht="14.25" customHeight="1"/>
+    <row r="349" ht="14.25" customHeight="1"/>
+    <row r="350" ht="14.25" customHeight="1"/>
+    <row r="351" ht="14.25" customHeight="1"/>
+    <row r="352" ht="14.25" customHeight="1"/>
+    <row r="353" ht="14.25" customHeight="1"/>
+    <row r="354" ht="14.25" customHeight="1"/>
+    <row r="355" ht="14.25" customHeight="1"/>
+    <row r="356" ht="14.25" customHeight="1"/>
+    <row r="357" ht="14.25" customHeight="1"/>
+    <row r="358" ht="14.25" customHeight="1"/>
+    <row r="359" ht="14.25" customHeight="1"/>
+    <row r="360" ht="14.25" customHeight="1"/>
+    <row r="361" ht="14.25" customHeight="1"/>
+    <row r="362" ht="14.25" customHeight="1"/>
+    <row r="363" ht="14.25" customHeight="1"/>
+    <row r="364" ht="14.25" customHeight="1"/>
+    <row r="365" ht="14.25" customHeight="1"/>
+    <row r="366" ht="14.25" customHeight="1"/>
+    <row r="367" ht="14.25" customHeight="1"/>
+    <row r="368" ht="14.25" customHeight="1"/>
+    <row r="369" ht="14.25" customHeight="1"/>
+    <row r="370" ht="14.25" customHeight="1"/>
+    <row r="371" ht="14.25" customHeight="1"/>
+    <row r="372" ht="14.25" customHeight="1"/>
+    <row r="373" ht="14.25" customHeight="1"/>
+    <row r="374" ht="14.25" customHeight="1"/>
+    <row r="375" ht="14.25" customHeight="1"/>
+    <row r="376" ht="14.25" customHeight="1"/>
+    <row r="377" ht="14.25" customHeight="1"/>
+    <row r="378" ht="14.25" customHeight="1"/>
+    <row r="379" ht="14.25" customHeight="1"/>
+    <row r="380" ht="14.25" customHeight="1"/>
+    <row r="381" ht="14.25" customHeight="1"/>
+    <row r="382" ht="14.25" customHeight="1"/>
+    <row r="383" ht="14.25" customHeight="1"/>
+    <row r="384" ht="14.25" customHeight="1"/>
+    <row r="385" ht="14.25" customHeight="1"/>
+    <row r="386" ht="14.25" customHeight="1"/>
+    <row r="387" ht="14.25" customHeight="1"/>
+    <row r="388" ht="14.25" customHeight="1"/>
+    <row r="389" ht="14.25" customHeight="1"/>
+    <row r="390" ht="14.25" customHeight="1"/>
+    <row r="391" ht="14.25" customHeight="1"/>
+    <row r="392" ht="14.25" customHeight="1"/>
+    <row r="393" ht="14.25" customHeight="1"/>
+    <row r="394" ht="14.25" customHeight="1"/>
+    <row r="395" ht="14.25" customHeight="1"/>
+    <row r="396" ht="14.25" customHeight="1"/>
+    <row r="397" ht="14.25" customHeight="1"/>
+    <row r="398" ht="14.25" customHeight="1"/>
+    <row r="399" ht="14.25" customHeight="1"/>
+    <row r="400" ht="14.25" customHeight="1"/>
+    <row r="401" ht="14.25" customHeight="1"/>
+    <row r="402" ht="14.25" customHeight="1"/>
+    <row r="403" ht="14.25" customHeight="1"/>
+    <row r="404" ht="14.25" customHeight="1"/>
+    <row r="405" ht="14.25" customHeight="1"/>
+    <row r="406" ht="14.25" customHeight="1"/>
+    <row r="407" ht="14.25" customHeight="1"/>
+    <row r="408" ht="14.25" customHeight="1"/>
+    <row r="409" ht="14.25" customHeight="1"/>
+    <row r="410" ht="14.25" customHeight="1"/>
+    <row r="411" ht="14.25" customHeight="1"/>
+    <row r="412" ht="14.25" customHeight="1"/>
+    <row r="413" ht="14.25" customHeight="1"/>
+    <row r="414" ht="14.25" customHeight="1"/>
+    <row r="415" ht="14.25" customHeight="1"/>
+    <row r="416" ht="14.25" customHeight="1"/>
+    <row r="417" ht="14.25" customHeight="1"/>
+    <row r="418" ht="14.25" customHeight="1"/>
+    <row r="419" ht="14.25" customHeight="1"/>
+    <row r="420" ht="14.25" customHeight="1"/>
+    <row r="421" ht="14.25" customHeight="1"/>
+    <row r="422" ht="14.25" customHeight="1"/>
+    <row r="423" ht="14.25" customHeight="1"/>
+    <row r="424" ht="14.25" customHeight="1"/>
+    <row r="425" ht="14.25" customHeight="1"/>
+    <row r="426" ht="14.25" customHeight="1"/>
+    <row r="427" ht="14.25" customHeight="1"/>
+    <row r="428" ht="14.25" customHeight="1"/>
+    <row r="429" ht="14.25" customHeight="1"/>
+    <row r="430" ht="14.25" customHeight="1"/>
+    <row r="431" ht="14.25" customHeight="1"/>
+    <row r="432" ht="14.25" customHeight="1"/>
+    <row r="433" ht="14.25" customHeight="1"/>
+    <row r="434" ht="14.25" customHeight="1"/>
+    <row r="435" ht="14.25" customHeight="1"/>
+    <row r="436" ht="14.25" customHeight="1"/>
+    <row r="437" ht="14.25" customHeight="1"/>
+    <row r="438" ht="14.25" customHeight="1"/>
+    <row r="439" ht="14.25" customHeight="1"/>
+    <row r="440" ht="14.25" customHeight="1"/>
+    <row r="441" ht="14.25" customHeight="1"/>
+    <row r="442" ht="14.25" customHeight="1"/>
+    <row r="443" ht="14.25" customHeight="1"/>
+    <row r="444" ht="14.25" customHeight="1"/>
+    <row r="445" ht="14.25" customHeight="1"/>
+    <row r="446" ht="14.25" customHeight="1"/>
+    <row r="447" ht="14.25" customHeight="1"/>
+    <row r="448" ht="14.25" customHeight="1"/>
+    <row r="449" ht="14.25" customHeight="1"/>
+    <row r="450" ht="14.25" customHeight="1"/>
+    <row r="451" ht="14.25" customHeight="1"/>
+    <row r="452" ht="14.25" customHeight="1"/>
+    <row r="453" ht="14.25" customHeight="1"/>
+    <row r="454" ht="14.25" customHeight="1"/>
+    <row r="455" ht="14.25" customHeight="1"/>
+    <row r="456" ht="14.25" customHeight="1"/>
+    <row r="457" ht="14.25" customHeight="1"/>
+    <row r="458" ht="14.25" customHeight="1"/>
+    <row r="459" ht="14.25" customHeight="1"/>
+    <row r="460" ht="14.25" customHeight="1"/>
+    <row r="461" ht="14.25" customHeight="1"/>
+    <row r="462" ht="14.25" customHeight="1"/>
+    <row r="463" ht="14.25" customHeight="1"/>
+    <row r="464" ht="14.25" customHeight="1"/>
+    <row r="465" ht="14.25" customHeight="1"/>
+    <row r="466" ht="14.25" customHeight="1"/>
+    <row r="467" ht="14.25" customHeight="1"/>
+    <row r="468" ht="14.25" customHeight="1"/>
+    <row r="469" ht="14.25" customHeight="1"/>
+    <row r="470" ht="14.25" customHeight="1"/>
+    <row r="471" ht="14.25" customHeight="1"/>
+    <row r="472" ht="14.25" customHeight="1"/>
+    <row r="473" ht="14.25" customHeight="1"/>
+    <row r="474" ht="14.25" customHeight="1"/>
+    <row r="475" ht="14.25" customHeight="1"/>
+    <row r="476" ht="14.25" customHeight="1"/>
+    <row r="477" ht="14.25" customHeight="1"/>
+    <row r="478" ht="14.25" customHeight="1"/>
+    <row r="479" ht="14.25" customHeight="1"/>
+    <row r="480" ht="14.25" customHeight="1"/>
+    <row r="481" ht="14.25" customHeight="1"/>
+    <row r="482" ht="14.25" customHeight="1"/>
+    <row r="483" ht="14.25" customHeight="1"/>
+    <row r="484" ht="14.25" customHeight="1"/>
+    <row r="485" ht="14.25" customHeight="1"/>
+    <row r="486" ht="14.25" customHeight="1"/>
+    <row r="487" ht="14.25" customHeight="1"/>
+    <row r="488" ht="14.25" customHeight="1"/>
+    <row r="489" ht="14.25" customHeight="1"/>
+    <row r="490" ht="14.25" customHeight="1"/>
+    <row r="491" ht="14.25" customHeight="1"/>
+    <row r="492" ht="14.25" customHeight="1"/>
+    <row r="493" ht="14.25" customHeight="1"/>
+    <row r="494" ht="14.25" customHeight="1"/>
+    <row r="495" ht="14.25" customHeight="1"/>
+    <row r="496" ht="14.25" customHeight="1"/>
+    <row r="497" ht="14.25" customHeight="1"/>
+    <row r="498" ht="14.25" customHeight="1"/>
+    <row r="499" ht="14.25" customHeight="1"/>
+    <row r="500" ht="14.25" customHeight="1"/>
+    <row r="501" ht="14.25" customHeight="1"/>
+    <row r="502" ht="14.25" customHeight="1"/>
+    <row r="503" ht="14.25" customHeight="1"/>
+    <row r="504" ht="14.25" customHeight="1"/>
+    <row r="505" ht="14.25" customHeight="1"/>
+    <row r="506" ht="14.25" customHeight="1"/>
+    <row r="507" ht="14.25" customHeight="1"/>
+    <row r="508" ht="14.25" customHeight="1"/>
+    <row r="509" ht="14.25" customHeight="1"/>
+    <row r="510" ht="14.25" customHeight="1"/>
+    <row r="511" ht="14.25" customHeight="1"/>
+    <row r="512" ht="14.25" customHeight="1"/>
+    <row r="513" ht="14.25" customHeight="1"/>
+    <row r="514" ht="14.25" customHeight="1"/>
+    <row r="515" ht="14.25" customHeight="1"/>
+    <row r="516" ht="14.25" customHeight="1"/>
+    <row r="517" ht="14.25" customHeight="1"/>
+    <row r="518" ht="14.25" customHeight="1"/>
+    <row r="519" ht="14.25" customHeight="1"/>
+    <row r="520" ht="14.25" customHeight="1"/>
+    <row r="521" ht="14.25" customHeight="1"/>
+    <row r="522" ht="14.25" customHeight="1"/>
+    <row r="523" ht="14.25" customHeight="1"/>
+    <row r="524" ht="14.25" customHeight="1"/>
+    <row r="525" ht="14.25" customHeight="1"/>
+    <row r="526" ht="14.25" customHeight="1"/>
+    <row r="527" ht="14.25" customHeight="1"/>
+    <row r="528" ht="14.25" customHeight="1"/>
+    <row r="529" ht="14.25" customHeight="1"/>
+    <row r="530" ht="14.25" customHeight="1"/>
+    <row r="531" ht="14.25" customHeight="1"/>
+    <row r="532" ht="14.25" customHeight="1"/>
+    <row r="533" ht="14.25" customHeight="1"/>
+    <row r="534" ht="14.25" customHeight="1"/>
+    <row r="535" ht="14.25" customHeight="1"/>
+    <row r="536" ht="14.25" customHeight="1"/>
+    <row r="537" ht="14.25" customHeight="1"/>
+    <row r="538" ht="14.25" customHeight="1"/>
+    <row r="539" ht="14.25" customHeight="1"/>
+    <row r="540" ht="14.25" customHeight="1"/>
+    <row r="541" ht="14.25" customHeight="1"/>
+    <row r="542" ht="14.25" customHeight="1"/>
+    <row r="543" ht="14.25" customHeight="1"/>
+    <row r="544" ht="14.25" customHeight="1"/>
+    <row r="545" ht="14.25" customHeight="1"/>
+    <row r="546" ht="14.25" customHeight="1"/>
+    <row r="547" ht="14.25" customHeight="1"/>
+    <row r="548" ht="14.25" customHeight="1"/>
+    <row r="549" ht="14.25" customHeight="1"/>
+    <row r="550" ht="14.25" customHeight="1"/>
+    <row r="551" ht="14.25" customHeight="1"/>
+    <row r="552" ht="14.25" customHeight="1"/>
+    <row r="553" ht="14.25" customHeight="1"/>
+    <row r="554" ht="14.25" customHeight="1"/>
+    <row r="555" ht="14.25" customHeight="1"/>
+    <row r="556" ht="14.25" customHeight="1"/>
+    <row r="557" ht="14.25" customHeight="1"/>
+    <row r="558" ht="14.25" customHeight="1"/>
+    <row r="559" ht="14.25" customHeight="1"/>
+    <row r="560" ht="14.25" customHeight="1"/>
+    <row r="561" ht="14.25" customHeight="1"/>
+    <row r="562" ht="14.25" customHeight="1"/>
+    <row r="563" ht="14.25" customHeight="1"/>
+    <row r="564" ht="14.25" customHeight="1"/>
+    <row r="565" ht="14.25" customHeight="1"/>
+    <row r="566" ht="14.25" customHeight="1"/>
+    <row r="567" ht="14.25" customHeight="1"/>
+    <row r="568" ht="14.25" customHeight="1"/>
+    <row r="569" ht="14.25" customHeight="1"/>
+    <row r="570" ht="14.25" customHeight="1"/>
+    <row r="571" ht="14.25" customHeight="1"/>
+    <row r="572" ht="14.25" customHeight="1"/>
+    <row r="573" ht="14.25" customHeight="1"/>
+    <row r="574" ht="14.25" customHeight="1"/>
+    <row r="575" ht="14.25" customHeight="1"/>
+    <row r="576" ht="14.25" customHeight="1"/>
+    <row r="577" ht="14.25" customHeight="1"/>
+    <row r="578" ht="14.25" customHeight="1"/>
+    <row r="579" ht="14.25" customHeight="1"/>
+    <row r="580" ht="14.25" customHeight="1"/>
+    <row r="581" ht="14.25" customHeight="1"/>
+    <row r="582" ht="14.25" customHeight="1"/>
+    <row r="583" ht="14.25" customHeight="1"/>
+    <row r="584" ht="14.25" customHeight="1"/>
+    <row r="585" ht="14.25" customHeight="1"/>
+    <row r="586" ht="14.25" customHeight="1"/>
+    <row r="587" ht="14.25" customHeight="1"/>
+    <row r="588" ht="14.25" customHeight="1"/>
+    <row r="589" ht="14.25" customHeight="1"/>
+    <row r="590" ht="14.25" customHeight="1"/>
+    <row r="591" ht="14.25" customHeight="1"/>
+    <row r="592" ht="14.25" customHeight="1"/>
+    <row r="593" ht="14.25" customHeight="1"/>
+    <row r="594" ht="14.25" customHeight="1"/>
+    <row r="595" ht="14.25" customHeight="1"/>
+    <row r="596" ht="14.25" customHeight="1"/>
+    <row r="597" ht="14.25" customHeight="1"/>
+    <row r="598" ht="14.25" customHeight="1"/>
+    <row r="599" ht="14.25" customHeight="1"/>
+    <row r="600" ht="14.25" customHeight="1"/>
+    <row r="601" ht="14.25" customHeight="1"/>
+    <row r="602" ht="14.25" customHeight="1"/>
+    <row r="603" ht="14.25" customHeight="1"/>
+    <row r="604" ht="14.25" customHeight="1"/>
+    <row r="605" ht="14.25" customHeight="1"/>
+    <row r="606" ht="14.25" customHeight="1"/>
+    <row r="607" ht="14.25" customHeight="1"/>
+    <row r="608" ht="14.25" customHeight="1"/>
+    <row r="609" ht="14.25" customHeight="1"/>
+    <row r="610" ht="14.25" customHeight="1"/>
+    <row r="611" ht="14.25" customHeight="1"/>
+    <row r="612" ht="14.25" customHeight="1"/>
+    <row r="613" ht="14.25" customHeight="1"/>
+    <row r="614" ht="14.25" customHeight="1"/>
+    <row r="615" ht="14.25" customHeight="1"/>
+    <row r="616" ht="14.25" customHeight="1"/>
+    <row r="617" ht="14.25" customHeight="1"/>
+    <row r="618" ht="14.25" customHeight="1"/>
+    <row r="619" ht="14.25" customHeight="1"/>
+    <row r="620" ht="14.25" customHeight="1"/>
+    <row r="621" ht="14.25" customHeight="1"/>
+    <row r="622" ht="14.25" customHeight="1"/>
+    <row r="623" ht="14.25" customHeight="1"/>
+    <row r="624" ht="14.25" customHeight="1"/>
+    <row r="625" ht="14.25" customHeight="1"/>
+    <row r="626" ht="14.25" customHeight="1"/>
+    <row r="627" ht="14.25" customHeight="1"/>
+    <row r="628" ht="14.25" customHeight="1"/>
+    <row r="629" ht="14.25" customHeight="1"/>
+    <row r="630" ht="14.25" customHeight="1"/>
+    <row r="631" ht="14.25" customHeight="1"/>
+    <row r="632" ht="14.25" customHeight="1"/>
+    <row r="633" ht="14.25" customHeight="1"/>
+    <row r="634" ht="14.25" customHeight="1"/>
+    <row r="635" ht="14.25" customHeight="1"/>
+    <row r="636" ht="14.25" customHeight="1"/>
+    <row r="637" ht="14.25" customHeight="1"/>
+    <row r="638" ht="14.25" customHeight="1"/>
+    <row r="639" ht="14.25" customHeight="1"/>
+    <row r="640" ht="14.25" customHeight="1"/>
+    <row r="641" ht="14.25" customHeight="1"/>
+    <row r="642" ht="14.25" customHeight="1"/>
+    <row r="643" ht="14.25" customHeight="1"/>
+    <row r="644" ht="14.25" customHeight="1"/>
+    <row r="645" ht="14.25" customHeight="1"/>
+    <row r="646" ht="14.25" customHeight="1"/>
+    <row r="647" ht="14.25" customHeight="1"/>
+    <row r="648" ht="14.25" customHeight="1"/>
+    <row r="649" ht="14.25" customHeight="1"/>
+    <row r="650" ht="14.25" customHeight="1"/>
+    <row r="651" ht="14.25" customHeight="1"/>
+    <row r="652" ht="14.25" customHeight="1"/>
+    <row r="653" ht="14.25" customHeight="1"/>
+    <row r="654" ht="14.25" customHeight="1"/>
+    <row r="655" ht="14.25" customHeight="1"/>
+    <row r="656" ht="14.25" customHeight="1"/>
+    <row r="657" ht="14.25" customHeight="1"/>
+    <row r="658" ht="14.25" customHeight="1"/>
+    <row r="659" ht="14.25" customHeight="1"/>
+    <row r="660" ht="14.25" customHeight="1"/>
+    <row r="661" ht="14.25" customHeight="1"/>
+    <row r="662" ht="14.25" customHeight="1"/>
+    <row r="663" ht="14.25" customHeight="1"/>
+    <row r="664" ht="14.25" customHeight="1"/>
+    <row r="665" ht="14.25" customHeight="1"/>
+    <row r="666" ht="14.25" customHeight="1"/>
+    <row r="667" ht="14.25" customHeight="1"/>
+    <row r="668" ht="14.25" customHeight="1"/>
+    <row r="669" ht="14.25" customHeight="1"/>
+    <row r="670" ht="14.25" customHeight="1"/>
+    <row r="671" ht="14.25" customHeight="1"/>
+    <row r="672" ht="14.25" customHeight="1"/>
+    <row r="673" ht="14.25" customHeight="1"/>
+    <row r="674" ht="14.25" customHeight="1"/>
+    <row r="675" ht="14.25" customHeight="1"/>
+    <row r="676" ht="14.25" customHeight="1"/>
+    <row r="677" ht="14.25" customHeight="1"/>
+    <row r="678" ht="14.25" customHeight="1"/>
+    <row r="679" ht="14.25" customHeight="1"/>
+    <row r="680" ht="14.25" customHeight="1"/>
+    <row r="681" ht="14.25" customHeight="1"/>
+    <row r="682" ht="14.25" customHeight="1"/>
+    <row r="683" ht="14.25" customHeight="1"/>
+    <row r="684" ht="14.25" customHeight="1"/>
+    <row r="685" ht="14.25" customHeight="1"/>
+    <row r="686" ht="14.25" customHeight="1"/>
+    <row r="687" ht="14.25" customHeight="1"/>
+    <row r="688" ht="14.25" customHeight="1"/>
+    <row r="689" ht="14.25" customHeight="1"/>
+    <row r="690" ht="14.25" customHeight="1"/>
+    <row r="691" ht="14.25" customHeight="1"/>
+    <row r="692" ht="14.25" customHeight="1"/>
+    <row r="693" ht="14.25" customHeight="1"/>
+    <row r="694" ht="14.25" customHeight="1"/>
+    <row r="695" ht="14.25" customHeight="1"/>
+    <row r="696" ht="14.25" customHeight="1"/>
+    <row r="697" ht="14.25" customHeight="1"/>
+    <row r="698" ht="14.25" customHeight="1"/>
+    <row r="699" ht="14.25" customHeight="1"/>
+    <row r="700" ht="14.25" customHeight="1"/>
+    <row r="701" ht="14.25" customHeight="1"/>
+    <row r="702" ht="14.25" customHeight="1"/>
+    <row r="703" ht="14.25" customHeight="1"/>
+    <row r="704" ht="14.25" customHeight="1"/>
+    <row r="705" ht="14.25" customHeight="1"/>
+    <row r="706" ht="14.25" customHeight="1"/>
+    <row r="707" ht="14.25" customHeight="1"/>
+    <row r="708" ht="14.25" customHeight="1"/>
+    <row r="709" ht="14.25" customHeight="1"/>
+    <row r="710" ht="14.25" customHeight="1"/>
+    <row r="711" ht="14.25" customHeight="1"/>
+    <row r="712" ht="14.25" customHeight="1"/>
+    <row r="713" ht="14.25" customHeight="1"/>
+    <row r="714" ht="14.25" customHeight="1"/>
+    <row r="715" ht="14.25" customHeight="1"/>
+    <row r="716" ht="14.25" customHeight="1"/>
+    <row r="717" ht="14.25" customHeight="1"/>
+    <row r="718" ht="14.25" customHeight="1"/>
+    <row r="719" ht="14.25" customHeight="1"/>
+    <row r="720" ht="14.25" customHeight="1"/>
+    <row r="721" ht="14.25" customHeight="1"/>
+    <row r="722" ht="14.25" customHeight="1"/>
+    <row r="723" ht="14.25" customHeight="1"/>
+    <row r="724" ht="14.25" customHeight="1"/>
+    <row r="725" ht="14.25" customHeight="1"/>
+    <row r="726" ht="14.25" customHeight="1"/>
+    <row r="727" ht="14.25" customHeight="1"/>
+    <row r="728" ht="14.25" customHeight="1"/>
+    <row r="729" ht="14.25" customHeight="1"/>
+    <row r="730" ht="14.25" customHeight="1"/>
+    <row r="731" ht="14.25" customHeight="1"/>
+    <row r="732" ht="14.25" customHeight="1"/>
+    <row r="733" ht="14.25" customHeight="1"/>
+    <row r="734" ht="14.25" customHeight="1"/>
+    <row r="735" ht="14.25" customHeight="1"/>
+    <row r="736" ht="14.25" customHeight="1"/>
+    <row r="737" ht="14.25" customHeight="1"/>
+    <row r="738" ht="14.25" customHeight="1"/>
+    <row r="739" ht="14.25" customHeight="1"/>
+    <row r="740" ht="14.25" customHeight="1"/>
+    <row r="741" ht="14.25" customHeight="1"/>
+    <row r="742" ht="14.25" customHeight="1"/>
+    <row r="743" ht="14.25" customHeight="1"/>
+    <row r="744" ht="14.25" customHeight="1"/>
+    <row r="745" ht="14.25" customHeight="1"/>
+    <row r="746" ht="14.25" customHeight="1"/>
+    <row r="747" ht="14.25" customHeight="1"/>
+    <row r="748" ht="14.25" customHeight="1"/>
+    <row r="749" ht="14.25" customHeight="1"/>
+    <row r="750" ht="14.25" customHeight="1"/>
+    <row r="751" ht="14.25" customHeight="1"/>
+    <row r="752" ht="14.25" customHeight="1"/>
+    <row r="753" ht="14.25" customHeight="1"/>
+    <row r="754" ht="14.25" customHeight="1"/>
+    <row r="755" ht="14.25" customHeight="1"/>
+    <row r="756" ht="14.25" customHeight="1"/>
+    <row r="757" ht="14.25" customHeight="1"/>
+    <row r="758" ht="14.25" customHeight="1"/>
+    <row r="759" ht="14.25" customHeight="1"/>
+    <row r="760" ht="14.25" customHeight="1"/>
+    <row r="761" ht="14.25" customHeight="1"/>
+    <row r="762" ht="14.25" customHeight="1"/>
+    <row r="763" ht="14.25" customHeight="1"/>
+    <row r="764" ht="14.25" customHeight="1"/>
+    <row r="765" ht="14.25" customHeight="1"/>
+    <row r="766" ht="14.25" customHeight="1"/>
+    <row r="767" ht="14.25" customHeight="1"/>
+    <row r="768" ht="14.25" customHeight="1"/>
+    <row r="769" ht="14.25" customHeight="1"/>
+    <row r="770" ht="14.25" customHeight="1"/>
+    <row r="771" ht="14.25" customHeight="1"/>
+    <row r="772" ht="14.25" customHeight="1"/>
+    <row r="773" ht="14.25" customHeight="1"/>
+    <row r="774" ht="14.25" customHeight="1"/>
+    <row r="775" ht="14.25" customHeight="1"/>
+    <row r="776" ht="14.25" customHeight="1"/>
+    <row r="777" ht="14.25" customHeight="1"/>
+    <row r="778" ht="14.25" customHeight="1"/>
+    <row r="779" ht="14.25" customHeight="1"/>
+    <row r="780" ht="14.25" customHeight="1"/>
+    <row r="781" ht="14.25" customHeight="1"/>
+    <row r="782" ht="14.25" customHeight="1"/>
+    <row r="783" ht="14.25" customHeight="1"/>
+    <row r="784" ht="14.25" customHeight="1"/>
+    <row r="785" ht="14.25" customHeight="1"/>
+    <row r="786" ht="14.25" customHeight="1"/>
+    <row r="787" ht="14.25" customHeight="1"/>
+    <row r="788" ht="14.25" customHeight="1"/>
+    <row r="789" ht="14.25" customHeight="1"/>
+    <row r="790" ht="14.25" customHeight="1"/>
+    <row r="791" ht="14.25" customHeight="1"/>
+    <row r="792" ht="14.25" customHeight="1"/>
+    <row r="793" ht="14.25" customHeight="1"/>
+    <row r="794" ht="14.25" customHeight="1"/>
+    <row r="795" ht="14.25" customHeight="1"/>
+    <row r="796" ht="14.25" customHeight="1"/>
+    <row r="797" ht="14.25" customHeight="1"/>
+    <row r="798" ht="14.25" customHeight="1"/>
+    <row r="799" ht="14.25" customHeight="1"/>
+    <row r="800" ht="14.25" customHeight="1"/>
+    <row r="801" ht="14.25" customHeight="1"/>
+    <row r="802" ht="14.25" customHeight="1"/>
+    <row r="803" ht="14.25" customHeight="1"/>
+    <row r="804" ht="14.25" customHeight="1"/>
+    <row r="805" ht="14.25" customHeight="1"/>
+    <row r="806" ht="14.25" customHeight="1"/>
+    <row r="807" ht="14.25" customHeight="1"/>
+    <row r="808" ht="14.25" customHeight="1"/>
+    <row r="809" ht="14.25" customHeight="1"/>
+    <row r="810" ht="14.25" customHeight="1"/>
+    <row r="811" ht="14.25" customHeight="1"/>
+    <row r="812" ht="14.25" customHeight="1"/>
+    <row r="813" ht="14.25" customHeight="1"/>
+    <row r="814" ht="14.25" customHeight="1"/>
+    <row r="815" ht="14.25" customHeight="1"/>
+    <row r="816" ht="14.25" customHeight="1"/>
+    <row r="817" ht="14.25" customHeight="1"/>
+    <row r="818" ht="14.25" customHeight="1"/>
+    <row r="819" ht="14.25" customHeight="1"/>
+    <row r="820" ht="14.25" customHeight="1"/>
+    <row r="821" ht="14.25" customHeight="1"/>
+    <row r="822" ht="14.25" customHeight="1"/>
+    <row r="823" ht="14.25" customHeight="1"/>
+    <row r="824" ht="14.25" customHeight="1"/>
+    <row r="825" ht="14.25" customHeight="1"/>
+    <row r="826" ht="14.25" customHeight="1"/>
+    <row r="827" ht="14.25" customHeight="1"/>
+    <row r="828" ht="14.25" customHeight="1"/>
+    <row r="829" ht="14.25" customHeight="1"/>
+    <row r="830" ht="14.25" customHeight="1"/>
+    <row r="831" ht="14.25" customHeight="1"/>
+    <row r="832" ht="14.25" customHeight="1"/>
+    <row r="833" ht="14.25" customHeight="1"/>
+    <row r="834" ht="14.25" customHeight="1"/>
+    <row r="835" ht="14.25" customHeight="1"/>
+    <row r="836" ht="14.25" customHeight="1"/>
+    <row r="837" ht="14.25" customHeight="1"/>
+    <row r="838" ht="14.25" customHeight="1"/>
+    <row r="839" ht="14.25" customHeight="1"/>
+    <row r="840" ht="14.25" customHeight="1"/>
+    <row r="841" ht="14.25" customHeight="1"/>
+    <row r="842" ht="14.25" customHeight="1"/>
+    <row r="843" ht="14.25" customHeight="1"/>
+    <row r="844" ht="14.25" customHeight="1"/>
+    <row r="845" ht="14.25" customHeight="1"/>
+    <row r="846" ht="14.25" customHeight="1"/>
+    <row r="847" ht="14.25" customHeight="1"/>
+    <row r="848" ht="14.25" customHeight="1"/>
+    <row r="849" ht="14.25" customHeight="1"/>
+    <row r="850" ht="14.25" customHeight="1"/>
+    <row r="851" ht="14.25" customHeight="1"/>
+    <row r="852" ht="14.25" customHeight="1"/>
+    <row r="853" ht="14.25" customHeight="1"/>
+    <row r="854" ht="14.25" customHeight="1"/>
+    <row r="855" ht="14.25" customHeight="1"/>
+    <row r="856" ht="14.25" customHeight="1"/>
+    <row r="857" ht="14.25" customHeight="1"/>
+    <row r="858" ht="14.25" customHeight="1"/>
+    <row r="859" ht="14.25" customHeight="1"/>
+    <row r="860" ht="14.25" customHeight="1"/>
+    <row r="861" ht="14.25" customHeight="1"/>
+    <row r="862" ht="14.25" customHeight="1"/>
+    <row r="863" ht="14.25" customHeight="1"/>
+    <row r="864" ht="14.25" customHeight="1"/>
+    <row r="865" ht="14.25" customHeight="1"/>
+    <row r="866" ht="14.25" customHeight="1"/>
+    <row r="867" ht="14.25" customHeight="1"/>
+    <row r="868" ht="14.25" customHeight="1"/>
+    <row r="869" ht="14.25" customHeight="1"/>
+    <row r="870" ht="14.25" customHeight="1"/>
+    <row r="871" ht="14.25" customHeight="1"/>
+    <row r="872" ht="14.25" customHeight="1"/>
+    <row r="873" ht="14.25" customHeight="1"/>
+    <row r="874" ht="14.25" customHeight="1"/>
+    <row r="875" ht="14.25" customHeight="1"/>
+    <row r="876" ht="14.25" customHeight="1"/>
+    <row r="877" ht="14.25" customHeight="1"/>
+    <row r="878" ht="14.25" customHeight="1"/>
+    <row r="879" ht="14.25" customHeight="1"/>
+    <row r="880" ht="14.25" customHeight="1"/>
+    <row r="881" ht="14.25" customHeight="1"/>
+    <row r="882" ht="14.25" customHeight="1"/>
+    <row r="883" ht="14.25" customHeight="1"/>
+    <row r="884" ht="14.25" customHeight="1"/>
+    <row r="885" ht="14.25" customHeight="1"/>
+    <row r="886" ht="14.25" customHeight="1"/>
+    <row r="887" ht="14.25" customHeight="1"/>
+    <row r="888" ht="14.25" customHeight="1"/>
+    <row r="889" ht="14.25" customHeight="1"/>
+    <row r="890" ht="14.25" customHeight="1"/>
+    <row r="891" ht="14.25" customHeight="1"/>
+    <row r="892" ht="14.25" customHeight="1"/>
+    <row r="893" ht="14.25" customHeight="1"/>
+    <row r="894" ht="14.25" customHeight="1"/>
+    <row r="895" ht="14.25" customHeight="1"/>
+    <row r="896" ht="14.25" customHeight="1"/>
+    <row r="897" ht="14.25" customHeight="1"/>
+    <row r="898" ht="14.25" customHeight="1"/>
+    <row r="899" ht="14.25" customHeight="1"/>
+    <row r="900" ht="14.25" customHeight="1"/>
+    <row r="901" ht="14.25" customHeight="1"/>
+    <row r="902" ht="14.25" customHeight="1"/>
+    <row r="903" ht="14.25" customHeight="1"/>
+    <row r="904" ht="14.25" customHeight="1"/>
+    <row r="905" ht="14.25" customHeight="1"/>
+    <row r="906" ht="14.25" customHeight="1"/>
+    <row r="907" ht="14.25" customHeight="1"/>
+    <row r="908" ht="14.25" customHeight="1"/>
+    <row r="909" ht="14.25" customHeight="1"/>
+    <row r="910" ht="14.25" customHeight="1"/>
+    <row r="911" ht="14.25" customHeight="1"/>
+    <row r="912" ht="14.25" customHeight="1"/>
+    <row r="913" ht="14.25" customHeight="1"/>
+    <row r="914" ht="14.25" customHeight="1"/>
+    <row r="915" ht="14.25" customHeight="1"/>
+    <row r="916" ht="14.25" customHeight="1"/>
+    <row r="917" ht="14.25" customHeight="1"/>
+    <row r="918" ht="14.25" customHeight="1"/>
+    <row r="919" ht="14.25" customHeight="1"/>
+    <row r="920" ht="14.25" customHeight="1"/>
+    <row r="921" ht="14.25" customHeight="1"/>
+    <row r="922" ht="14.25" customHeight="1"/>
+    <row r="923" ht="14.25" customHeight="1"/>
+    <row r="924" ht="14.25" customHeight="1"/>
+    <row r="925" ht="14.25" customHeight="1"/>
+    <row r="926" ht="14.25" customHeight="1"/>
+    <row r="927" ht="14.25" customHeight="1"/>
+    <row r="928" ht="14.25" customHeight="1"/>
+    <row r="929" ht="14.25" customHeight="1"/>
+    <row r="930" ht="14.25" customHeight="1"/>
+    <row r="931" ht="14.25" customHeight="1"/>
+    <row r="932" ht="14.25" customHeight="1"/>
+    <row r="933" ht="14.25" customHeight="1"/>
+    <row r="934" ht="14.25" customHeight="1"/>
+    <row r="935" ht="14.25" customHeight="1"/>
+    <row r="936" ht="14.25" customHeight="1"/>
+    <row r="937" ht="14.25" customHeight="1"/>
+    <row r="938" ht="14.25" customHeight="1"/>
+    <row r="939" ht="14.25" customHeight="1"/>
+    <row r="940" ht="14.25" customHeight="1"/>
+    <row r="941" ht="14.25" customHeight="1"/>
+    <row r="942" ht="14.25" customHeight="1"/>
+    <row r="943" ht="14.25" customHeight="1"/>
+    <row r="944" ht="14.25" customHeight="1"/>
+    <row r="945" ht="14.25" customHeight="1"/>
+    <row r="946" ht="14.25" customHeight="1"/>
+    <row r="947" ht="14.25" customHeight="1"/>
+    <row r="948" ht="14.25" customHeight="1"/>
+    <row r="949" ht="14.25" customHeight="1"/>
+    <row r="950" ht="14.25" customHeight="1"/>
+    <row r="951" ht="14.25" customHeight="1"/>
+    <row r="952" ht="14.25" customHeight="1"/>
+    <row r="953" ht="14.25" customHeight="1"/>
+    <row r="954" ht="14.25" customHeight="1"/>
+    <row r="955" ht="14.25" customHeight="1"/>
+    <row r="956" ht="14.25" customHeight="1"/>
+    <row r="957" ht="14.25" customHeight="1"/>
+    <row r="958" ht="14.25" customHeight="1"/>
+    <row r="959" ht="14.25" customHeight="1"/>
+    <row r="960" ht="14.25" customHeight="1"/>
+    <row r="961" ht="14.25" customHeight="1"/>
+    <row r="962" ht="14.25" customHeight="1"/>
+    <row r="963" ht="14.25" customHeight="1"/>
+    <row r="964" ht="14.25" customHeight="1"/>
+    <row r="965" ht="14.25" customHeight="1"/>
+    <row r="966" ht="14.25" customHeight="1"/>
+    <row r="967" ht="14.25" customHeight="1"/>
+    <row r="968" ht="14.25" customHeight="1"/>
+    <row r="969" ht="14.25" customHeight="1"/>
+    <row r="970" ht="14.25" customHeight="1"/>
+    <row r="971" ht="14.25" customHeight="1"/>
+    <row r="972" ht="14.25" customHeight="1"/>
+    <row r="973" ht="14.25" customHeight="1"/>
+    <row r="974" ht="14.25" customHeight="1"/>
+    <row r="975" ht="14.25" customHeight="1"/>
+    <row r="976" ht="14.25" customHeight="1"/>
+    <row r="977" ht="14.25" customHeight="1"/>
+    <row r="978" ht="14.25" customHeight="1"/>
+    <row r="979" ht="14.25" customHeight="1"/>
+    <row r="980" ht="14.25" customHeight="1"/>
+    <row r="981" ht="14.25" customHeight="1"/>
+    <row r="982" ht="14.25" customHeight="1"/>
+    <row r="983" ht="14.25" customHeight="1"/>
+    <row r="984" ht="14.25" customHeight="1"/>
+    <row r="985" ht="14.25" customHeight="1"/>
+    <row r="986" ht="14.25" customHeight="1"/>
+    <row r="987" ht="14.25" customHeight="1"/>
+    <row r="988" ht="14.25" customHeight="1"/>
+    <row r="989" ht="14.25" customHeight="1"/>
+    <row r="990" ht="14.25" customHeight="1"/>
+    <row r="991" ht="14.25" customHeight="1"/>
+    <row r="992" ht="14.25" customHeight="1"/>
+    <row r="993" ht="14.25" customHeight="1"/>
+    <row r="994" ht="14.25" customHeight="1"/>
+    <row r="995" ht="14.25" customHeight="1"/>
+    <row r="996" ht="14.25" customHeight="1"/>
+    <row r="997" ht="14.25" customHeight="1"/>
+    <row r="998" ht="14.25" customHeight="1"/>
+    <row r="999" ht="14.25" customHeight="1"/>
+    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A14:C14"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>